--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\Cisco\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C61FAA-921A-43F4-B5ED-BF2B6B78D2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D23B42-E0AA-45C6-9F40-BF2D30798091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="803" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="803" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN Summary" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="VLAN 100 - FW-NAT" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VLAN 10 - End Devices'!$A$4:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VLAN 10 - End Devices'!$A$5:$A$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'VLAN 20 - Servers'!$A$4:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'VLAN 30 - Security'!$A$4:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'VLAN 99 - Management'!$A$4:$N$36</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="284">
   <si>
     <t>Network Addressing Plan - VLAN Summary</t>
   </si>
@@ -259,9 +259,6 @@
     <t>Switch6</t>
   </si>
   <si>
-    <t>Fa0/2</t>
-  </si>
-  <si>
     <t>Printer0</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
     <t>Switch7</t>
   </si>
   <si>
-    <t>Fa0/1</t>
-  </si>
-  <si>
     <t>Laptop1</t>
   </si>
   <si>
@@ -715,15 +709,9 @@
     <t>192.168.10.26</t>
   </si>
   <si>
-    <t>192.168.10.27</t>
-  </si>
-  <si>
     <t>192.168.10.28</t>
   </si>
   <si>
-    <t>192.168.10.29</t>
-  </si>
-  <si>
     <t>192.168.10.30</t>
   </si>
   <si>
@@ -866,6 +854,51 @@
   </si>
   <si>
     <t>0001.645E.62B6</t>
+  </si>
+  <si>
+    <t>00E0.B095.E24C</t>
+  </si>
+  <si>
+    <t>192.168.20.16</t>
+  </si>
+  <si>
+    <t>00E0.A315.325B</t>
+  </si>
+  <si>
+    <t>192.169.30.17</t>
+  </si>
+  <si>
+    <t>0001.C771.5826</t>
+  </si>
+  <si>
+    <t>192.168.30.17/27</t>
+  </si>
+  <si>
+    <t>0001.6418.EE33</t>
+  </si>
+  <si>
+    <t>0060.2FC0.4A51</t>
+  </si>
+  <si>
+    <t>000A.4147.8CB3</t>
+  </si>
+  <si>
+    <t>0060.4773.30D4</t>
+  </si>
+  <si>
+    <t>0001.63E4.DBAA</t>
+  </si>
+  <si>
+    <t>192.168.20.10/24</t>
+  </si>
+  <si>
+    <t>192.168.20.11/24</t>
+  </si>
+  <si>
+    <t>000D.BDB3.26EA</t>
+  </si>
+  <si>
+    <t>0090.21B1.4B9C</t>
   </si>
 </sst>
 </file>
@@ -936,7 +969,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -989,6 +1022,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1056,7 +1101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1134,6 +1179,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1510,8 +1567,8 @@
       <c r="O5" s="8"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="5">
-        <f>COUNTA('VLAN 10 - End Devices'!B5:B73)</f>
-        <v>18</v>
+        <f>COUNTA('VLAN 10 - End Devices'!B5:B71)</f>
+        <v>16</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>22</v>
@@ -1542,7 +1599,7 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="5">
         <f>COUNTA('VLAN 20 - Servers'!B5:B80)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>25</v>
@@ -1573,7 +1630,7 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="5">
         <f>COUNTA('VLAN 30 - Security'!B5:B80)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>28</v>
@@ -1680,7 +1737,7 @@
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1866,29 +1923,29 @@
         <v>69</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" s="15">
         <v>10</v>
       </c>
       <c r="G8" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>211</v>
-      </c>
       <c r="J8" s="27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="15" t="s">
         <v>57</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N8" s="6"/>
     </row>
@@ -1897,26 +1954,26 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>71</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>72</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>69</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F9" s="15">
         <v>10</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9" s="13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J9" s="28"/>
       <c r="K9" s="13"/>
@@ -1924,7 +1981,7 @@
         <v>57</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N9" s="6"/>
     </row>
@@ -1933,26 +1990,26 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="D10" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>76</v>
-      </c>
       <c r="E10" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F10" s="15">
         <v>10</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="13" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J10" s="28"/>
       <c r="K10" s="13"/>
@@ -1960,7 +2017,7 @@
         <v>57</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N10" s="6"/>
     </row>
@@ -1969,26 +2026,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="15">
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="13"/>
@@ -1996,7 +2053,7 @@
         <v>57</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N11" s="6"/>
     </row>
@@ -2005,26 +2062,26 @@
         <v>13</v>
       </c>
       <c r="B12" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>86</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>88</v>
       </c>
       <c r="F12" s="21">
         <v>10</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="23" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="23"/>
@@ -2033,7 +2090,7 @@
       </c>
       <c r="M12" s="24"/>
       <c r="N12" s="25" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2041,26 +2098,26 @@
         <v>15</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13" s="15">
         <v>10</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="13"/>
@@ -2068,42 +2125,44 @@
         <v>57</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="15">
         <v>17</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F14" s="15">
         <v>10</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J14" s="28"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M14" s="17"/>
+      <c r="M14" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2111,33 +2170,35 @@
         <v>18</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F15" s="15">
         <v>10</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J15" s="28"/>
       <c r="K15" s="13"/>
       <c r="L15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M15" s="17"/>
+      <c r="M15" s="17" t="s">
+        <v>278</v>
+      </c>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2145,33 +2206,35 @@
         <v>19</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="15">
         <v>10</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J16" s="28"/>
       <c r="K16" s="13"/>
       <c r="L16" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="17"/>
+      <c r="M16" s="17" t="s">
+        <v>283</v>
+      </c>
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2179,212 +2242,180 @@
         <v>20</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F17" s="15">
         <v>10</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J17" s="28"/>
       <c r="K17" s="13"/>
       <c r="L17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M17" s="17"/>
+      <c r="M17" s="17" t="s">
+        <v>282</v>
+      </c>
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>100</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F18" s="15">
         <v>10</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J18" s="28"/>
       <c r="K18" s="13"/>
       <c r="L18" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M18" s="17"/>
+      <c r="M18" s="17" t="s">
+        <v>269</v>
+      </c>
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>102</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F19" s="15">
         <v>10</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H19" s="28"/>
       <c r="I19" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J19" s="28"/>
       <c r="K19" s="13"/>
       <c r="L19" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="17"/>
-      <c r="N19" s="6"/>
+      <c r="M19" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="N19" s="18" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F20" s="15">
         <v>10</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="H20" s="28"/>
+        <v>222</v>
+      </c>
+      <c r="H20" s="29"/>
       <c r="I20" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="J20" s="28"/>
+        <v>222</v>
+      </c>
+      <c r="J20" s="29"/>
       <c r="K20" s="13"/>
       <c r="L20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M20" s="17"/>
-      <c r="N20" s="6"/>
+      <c r="M20" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="N20" s="18" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15">
-        <v>24</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="15">
-        <v>10</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="N21" s="18" t="s">
-        <v>258</v>
-      </c>
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15">
-        <v>25</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F22" s="15">
-        <v>10</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="J22" s="29"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>258</v>
-      </c>
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="15"/>
@@ -2393,11 +2424,11 @@
       <c r="D23" s="16"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
@@ -2409,11 +2440,11 @@
       <c r="D24" s="16"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="6"/>
@@ -2425,11 +2456,11 @@
       <c r="D25" s="16"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="6"/>
@@ -2441,11 +2472,11 @@
       <c r="D26" s="16"/>
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="6"/>
@@ -2457,11 +2488,11 @@
       <c r="D27" s="16"/>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="6"/>
@@ -2473,11 +2504,11 @@
       <c r="D28" s="16"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="6"/>
@@ -2489,11 +2520,11 @@
       <c r="D29" s="16"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="6"/>
@@ -2505,52 +2536,20 @@
       <c r="D30" s="16"/>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="6"/>
-    </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="15"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:N32" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A5:A20" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="2">
-    <mergeCell ref="H8:H22"/>
-    <mergeCell ref="J8:J22"/>
+    <mergeCell ref="H8:H20"/>
+    <mergeCell ref="J8:J20"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2582,12 +2581,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2653,7 +2652,7 @@
         <v>55</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F5" s="11">
         <v>20</v>
@@ -2685,7 +2684,7 @@
         <v>61</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F6" s="11">
         <v>20</v>
@@ -2717,7 +2716,7 @@
         <v>65</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F7" s="11">
         <v>20</v>
@@ -2740,36 +2739,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" s="15">
         <v>20</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" s="13"/>
+        <v>208</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>280</v>
+      </c>
       <c r="J8" s="27" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="15" t="s">
         <v>62</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="N8" s="6"/>
     </row>
@@ -2778,32 +2779,34 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>116</v>
-      </c>
       <c r="E9" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="15">
         <v>20</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H9" s="28"/>
-      <c r="I9" s="13"/>
+      <c r="I9" s="13" t="s">
+        <v>281</v>
+      </c>
       <c r="J9" s="28"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N9" s="6"/>
     </row>
@@ -2812,32 +2815,34 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F10" s="15">
         <v>20</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H10" s="28"/>
-      <c r="I10" s="13"/>
+      <c r="I10" s="13" t="s">
+        <v>243</v>
+      </c>
       <c r="J10" s="28"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N10" s="6"/>
     </row>
@@ -2846,32 +2851,34 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="15">
         <v>20</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H11" s="28"/>
-      <c r="I11" s="13"/>
+      <c r="I11" s="13" t="s">
+        <v>244</v>
+      </c>
       <c r="J11" s="28"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N11" s="6"/>
     </row>
@@ -2880,31 +2887,35 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F12" s="15">
         <v>20</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H12" s="28"/>
-      <c r="I12" s="13"/>
+      <c r="I12" s="13" t="s">
+        <v>245</v>
+      </c>
       <c r="J12" s="28"/>
       <c r="K12" s="13"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="17"/>
+      <c r="M12" s="17" t="s">
+        <v>275</v>
+      </c>
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2912,47 +2923,71 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="F13" s="15">
         <v>20</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="29"/>
+        <v>246</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="I13" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="J13" s="28"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="17"/>
+      <c r="M13" s="17" t="s">
+        <v>279</v>
+      </c>
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
+      <c r="A14" s="15">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="15">
+        <v>20</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="J14" s="29"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
+      <c r="L14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="30" t="s">
+        <v>271</v>
+      </c>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2962,11 +2997,11 @@
       <c r="D15" s="16"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
@@ -2978,11 +3013,11 @@
       <c r="D16" s="16"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
@@ -2994,11 +3029,11 @@
       <c r="D17" s="16"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
@@ -3010,11 +3045,11 @@
       <c r="D18" s="16"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="6"/>
@@ -3026,11 +3061,11 @@
       <c r="D19" s="16"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
       <c r="N19" s="6"/>
@@ -3042,11 +3077,11 @@
       <c r="D20" s="16"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="6"/>
@@ -3058,11 +3093,11 @@
       <c r="D21" s="16"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
@@ -3074,11 +3109,11 @@
       <c r="D22" s="16"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
@@ -3090,11 +3125,11 @@
       <c r="D23" s="16"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
@@ -3102,8 +3137,8 @@
   </sheetData>
   <autoFilter ref="A4:N23" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="2">
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="J8:J13"/>
+    <mergeCell ref="H8:H14"/>
+    <mergeCell ref="J8:J14"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3135,12 +3170,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3206,7 +3241,7 @@
         <v>55</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F5" s="11">
         <v>30</v>
@@ -3238,7 +3273,7 @@
         <v>61</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F6" s="11">
         <v>30</v>
@@ -3270,7 +3305,7 @@
         <v>65</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F7" s="11">
         <v>30</v>
@@ -3293,38 +3328,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F8" s="15">
         <v>30</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="15" t="s">
         <v>62</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N8" s="6"/>
     </row>
@@ -3333,26 +3368,26 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>76</v>
-      </c>
       <c r="E9" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="15">
         <v>30</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9" s="13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J9" s="28"/>
       <c r="K9" s="13"/>
@@ -3360,7 +3395,7 @@
         <v>62</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N9" s="6"/>
     </row>
@@ -3369,26 +3404,26 @@
         <v>6</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F10" s="15">
         <v>30</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J10" s="28"/>
       <c r="K10" s="13"/>
@@ -3396,7 +3431,7 @@
         <v>62</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N10" s="6"/>
     </row>
@@ -3405,26 +3440,26 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F11" s="15">
         <v>30</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="13" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="13"/>
@@ -3432,7 +3467,7 @@
         <v>62</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N11" s="6"/>
     </row>
@@ -3441,26 +3476,26 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F12" s="15">
         <v>30</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="13" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="13"/>
@@ -3468,7 +3503,7 @@
         <v>62</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N12" s="6"/>
     </row>
@@ -3477,31 +3512,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F13" s="15">
         <v>30</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="13" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="17"/>
+      <c r="L13" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>276</v>
+      </c>
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3509,48 +3548,71 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F14" s="15">
         <v>30</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="13" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J14" s="28"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="15"/>
+      <c r="L14" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="M14" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="15">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" s="15">
+        <v>30</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="13"/>
       <c r="H15" s="28"/>
-      <c r="I15" s="13"/>
+      <c r="I15" s="13" t="s">
+        <v>274</v>
+      </c>
       <c r="J15" s="28"/>
       <c r="K15" s="13"/>
-      <c r="M15" s="17"/>
+      <c r="L15" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>273</v>
+      </c>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3560,13 +3622,13 @@
       <c r="D16" s="16"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="13"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="15"/>
-      <c r="M16" s="17"/>
+      <c r="M16" s="15"/>
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3576,13 +3638,13 @@
       <c r="D17" s="16"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="13"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="15"/>
-      <c r="M17" s="17"/>
+      <c r="M17" s="15"/>
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3592,13 +3654,13 @@
       <c r="D18" s="16"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="13"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="15"/>
-      <c r="M18" s="17"/>
+      <c r="M18" s="15"/>
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3608,20 +3670,20 @@
       <c r="D19" s="16"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="13"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="15"/>
-      <c r="M19" s="17"/>
+      <c r="M19" s="15"/>
       <c r="N19" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N19" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="2">
-    <mergeCell ref="J8:J19"/>
-    <mergeCell ref="H8:H19"/>
+    <mergeCell ref="H8:H15"/>
+    <mergeCell ref="J8:J15"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3653,17 +3715,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3671,22 +3733,22 @@
         <v>43</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>7</v>
@@ -3698,13 +3760,13 @@
         <v>50</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>19</v>
@@ -3721,10 +3783,10 @@
         <v>54</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F5" s="11">
         <v>99</v>
@@ -3737,13 +3799,13 @@
         <v>55</v>
       </c>
       <c r="L5" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3751,16 +3813,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="E6" s="16" t="s">
         <v>138</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>140</v>
       </c>
       <c r="F6" s="15">
         <v>99</v>
@@ -3773,10 +3835,10 @@
         <v>61</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N6" s="16"/>
     </row>
@@ -3785,16 +3847,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>138</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>140</v>
       </c>
       <c r="F7" s="15">
         <v>99</v>
@@ -3807,10 +3869,10 @@
         <v>65</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N7" s="16"/>
     </row>
@@ -3822,13 +3884,13 @@
         <v>61</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F8" s="15">
         <v>99</v>
@@ -3838,16 +3900,16 @@
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3858,13 +3920,13 @@
         <v>65</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F9" s="15">
         <v>99</v>
@@ -3874,16 +3936,16 @@
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3891,16 +3953,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>148</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>150</v>
       </c>
       <c r="F10" s="15">
         <v>99</v>
@@ -3913,10 +3975,10 @@
         <v>61</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N10" s="16"/>
     </row>
@@ -3925,16 +3987,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F11" s="15">
         <v>99</v>
@@ -3947,10 +4009,10 @@
         <v>65</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N11" s="16"/>
     </row>
@@ -3959,16 +4021,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F12" s="15">
         <v>99</v>
@@ -3978,13 +4040,13 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N12" s="16"/>
     </row>
@@ -3993,16 +4055,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F13" s="15">
         <v>99</v>
@@ -4012,13 +4074,13 @@
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
       <c r="K13" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N13" s="16"/>
     </row>
@@ -4027,16 +4089,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F14" s="15">
         <v>99</v>
@@ -4049,10 +4111,10 @@
         <v>61</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N14" s="16"/>
     </row>
@@ -4061,16 +4123,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F15" s="15">
         <v>99</v>
@@ -4083,10 +4145,10 @@
         <v>65</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N15" s="16"/>
     </row>
@@ -4095,16 +4157,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F16" s="15">
         <v>99</v>
@@ -4114,13 +4176,13 @@
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N16" s="16"/>
     </row>
@@ -4129,16 +4191,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F17" s="15">
         <v>99</v>
@@ -4148,13 +4210,13 @@
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N17" s="16"/>
     </row>
@@ -4166,13 +4228,13 @@
         <v>69</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F18" s="15">
         <v>99</v>
@@ -4182,13 +4244,13 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N18" s="16"/>
     </row>
@@ -4197,16 +4259,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F19" s="15">
         <v>99</v>
@@ -4219,10 +4281,10 @@
         <v>69</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N19" s="16"/>
     </row>
@@ -4231,16 +4293,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C20" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F20" s="15">
         <v>99</v>
@@ -4250,13 +4312,13 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N20" s="16"/>
     </row>
@@ -4265,16 +4327,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C21" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F21" s="15">
         <v>99</v>
@@ -4284,13 +4346,13 @@
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N21" s="16"/>
     </row>
@@ -4299,16 +4361,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F22" s="15">
         <v>99</v>
@@ -4318,13 +4380,13 @@
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M22" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N22" s="16"/>
     </row>
@@ -4333,16 +4395,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C23" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F23" s="15">
         <v>99</v>
@@ -4352,13 +4414,13 @@
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N23" s="16"/>
     </row>
@@ -4367,16 +4429,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C24" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F24" s="15">
         <v>99</v>
@@ -4386,13 +4448,13 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N24" s="16"/>
     </row>
@@ -4401,16 +4463,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C25" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F25" s="15">
         <v>99</v>
@@ -4420,13 +4482,13 @@
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
       <c r="K25" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N25" s="16"/>
     </row>
@@ -4435,16 +4497,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C26" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F26" s="15">
         <v>99</v>
@@ -4454,13 +4516,13 @@
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N26" s="16"/>
     </row>
@@ -4469,16 +4531,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C27" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="F27" s="15">
         <v>99</v>
@@ -4488,13 +4550,13 @@
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N27" s="16"/>
     </row>
@@ -4503,16 +4565,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C28" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>165</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>167</v>
       </c>
       <c r="F28" s="15">
         <v>99</v>
@@ -4522,16 +4584,16 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M28" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N28" s="16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4693,12 +4755,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4755,16 +4817,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="F5" s="11">
         <v>100</v>
@@ -4779,7 +4841,7 @@
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4787,16 +4849,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F6" s="11">
         <v>100</v>
@@ -4811,7 +4873,7 @@
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4819,16 +4881,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F7" s="11">
         <v>100</v>
@@ -4843,7 +4905,7 @@
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4851,16 +4913,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F8" s="15">
         <v>100</v>
@@ -4875,7 +4937,7 @@
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4883,16 +4945,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F9" s="15">
         <v>100</v>
@@ -4907,7 +4969,7 @@
       </c>
       <c r="M9" s="17"/>
       <c r="N9" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4976,7 +5038,7 @@
     </row>
     <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4984,25 +5046,25 @@
         <v>43</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>19</v>
@@ -5013,24 +5075,24 @@
         <v>1</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5038,24 +5100,24 @@
         <v>2</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5063,24 +5125,24 @@
         <v>3</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5088,24 +5150,24 @@
         <v>4</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5113,29 +5175,29 @@
         <v>5</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D23B42-E0AA-45C6-9F40-BF2D30798091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32DDD1E-A823-4633-A374-666D93303B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="803" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="803" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN Summary" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="307">
   <si>
     <t>Network Addressing Plan - VLAN Summary</t>
   </si>
@@ -899,6 +899,75 @@
   </si>
   <si>
     <t>0090.21B1.4B9C</t>
+  </si>
+  <si>
+    <t>192.168.99.1</t>
+  </si>
+  <si>
+    <t>192.168.99.2</t>
+  </si>
+  <si>
+    <t>192.168.99.11</t>
+  </si>
+  <si>
+    <t>192.168.99.12</t>
+  </si>
+  <si>
+    <t>192.168.99.21</t>
+  </si>
+  <si>
+    <t>192.168.99.22</t>
+  </si>
+  <si>
+    <t>192.168.99.23</t>
+  </si>
+  <si>
+    <t>192.168.99.24</t>
+  </si>
+  <si>
+    <t>192.168.99.25</t>
+  </si>
+  <si>
+    <t>192.168.99.26</t>
+  </si>
+  <si>
+    <t>192.168.99.27</t>
+  </si>
+  <si>
+    <t>192.168.99.28</t>
+  </si>
+  <si>
+    <t>192.168.99.31</t>
+  </si>
+  <si>
+    <t>192.168.99.32</t>
+  </si>
+  <si>
+    <t>192.168.99.33</t>
+  </si>
+  <si>
+    <t>192.168.99.34</t>
+  </si>
+  <si>
+    <t>192.168.99.35</t>
+  </si>
+  <si>
+    <t>192.168.99.36</t>
+  </si>
+  <si>
+    <t>192.168.99.37</t>
+  </si>
+  <si>
+    <t>192.168.99.38</t>
+  </si>
+  <si>
+    <t>192.168.99.39</t>
+  </si>
+  <si>
+    <t>192.168.99.40</t>
+  </si>
+  <si>
+    <t>NO IP, BUT BOTH THE DEVICES CONNECTED ARE ON VLAN 10</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1106,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1097,11 +1166,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1171,15 +1249,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1191,6 +1260,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1931,13 +2021,13 @@
       <c r="G8" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="31" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="31" t="s">
         <v>225</v>
       </c>
       <c r="K8" s="13"/>
@@ -1971,11 +2061,11 @@
       <c r="G9" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="32"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>57</v>
@@ -2007,11 +2097,11 @@
       <c r="G10" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="J10" s="28"/>
+      <c r="J10" s="32"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>57</v>
@@ -2043,11 +2133,11 @@
       <c r="G11" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="J11" s="28"/>
+      <c r="J11" s="32"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>57</v>
@@ -2079,11 +2169,11 @@
       <c r="G12" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="32"/>
       <c r="I12" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="J12" s="28"/>
+      <c r="J12" s="32"/>
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="s">
         <v>57</v>
@@ -2115,11 +2205,11 @@
       <c r="G13" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="J13" s="28"/>
+      <c r="J13" s="32"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>57</v>
@@ -2151,11 +2241,11 @@
       <c r="G14" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="32"/>
       <c r="I14" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="J14" s="28"/>
+      <c r="J14" s="32"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>57</v>
@@ -2187,11 +2277,11 @@
       <c r="G15" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="32"/>
       <c r="I15" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="J15" s="28"/>
+      <c r="J15" s="32"/>
       <c r="K15" s="13"/>
       <c r="L15" s="15" t="s">
         <v>57</v>
@@ -2223,11 +2313,11 @@
       <c r="G16" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="32"/>
       <c r="I16" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="J16" s="28"/>
+      <c r="J16" s="32"/>
       <c r="K16" s="13"/>
       <c r="L16" s="15" t="s">
         <v>57</v>
@@ -2259,11 +2349,11 @@
       <c r="G17" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="32"/>
       <c r="I17" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="J17" s="28"/>
+      <c r="J17" s="32"/>
       <c r="K17" s="13"/>
       <c r="L17" s="15" t="s">
         <v>57</v>
@@ -2295,11 +2385,11 @@
       <c r="G18" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="32"/>
       <c r="I18" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="J18" s="28"/>
+      <c r="J18" s="32"/>
       <c r="K18" s="13"/>
       <c r="L18" s="15" t="s">
         <v>57</v>
@@ -2331,11 +2421,11 @@
       <c r="G19" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="32"/>
       <c r="I19" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="J19" s="28"/>
+      <c r="J19" s="32"/>
       <c r="K19" s="13"/>
       <c r="L19" s="15" t="s">
         <v>57</v>
@@ -2369,11 +2459,11 @@
       <c r="G20" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="29"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="J20" s="29"/>
+      <c r="J20" s="33"/>
       <c r="K20" s="13"/>
       <c r="L20" s="15" t="s">
         <v>57</v>
@@ -2392,11 +2482,11 @@
       <c r="D21" s="16"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
@@ -2408,11 +2498,11 @@
       <c r="D22" s="16"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
@@ -2424,11 +2514,11 @@
       <c r="D23" s="16"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
@@ -2440,11 +2530,11 @@
       <c r="D24" s="16"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="6"/>
@@ -2456,11 +2546,11 @@
       <c r="D25" s="16"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="6"/>
@@ -2472,11 +2562,11 @@
       <c r="D26" s="16"/>
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="6"/>
@@ -2488,11 +2578,11 @@
       <c r="D27" s="16"/>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="6"/>
@@ -2504,11 +2594,11 @@
       <c r="D28" s="16"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="6"/>
@@ -2520,11 +2610,11 @@
       <c r="D29" s="16"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="6"/>
@@ -2536,11 +2626,11 @@
       <c r="D30" s="16"/>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="6"/>
@@ -2756,13 +2846,13 @@
       <c r="G8" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="31" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="31" t="s">
         <v>247</v>
       </c>
       <c r="K8" s="13"/>
@@ -2796,11 +2886,11 @@
       <c r="G9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="32"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
@@ -2832,11 +2922,11 @@
       <c r="G10" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="J10" s="28"/>
+      <c r="J10" s="32"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
@@ -2868,11 +2958,11 @@
       <c r="G11" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="J11" s="28"/>
+      <c r="J11" s="32"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
@@ -2904,11 +2994,11 @@
       <c r="G12" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="32"/>
       <c r="I12" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="J12" s="28"/>
+      <c r="J12" s="32"/>
       <c r="K12" s="13"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
@@ -2940,11 +3030,11 @@
       <c r="G13" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="J13" s="28"/>
+      <c r="J13" s="32"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
@@ -2976,16 +3066,16 @@
       <c r="G14" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="J14" s="29"/>
+      <c r="J14" s="33"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="30" t="s">
+      <c r="M14" s="27" t="s">
         <v>271</v>
       </c>
       <c r="N14" s="6"/>
@@ -2997,11 +3087,11 @@
       <c r="D15" s="16"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="6"/>
@@ -3013,11 +3103,11 @@
       <c r="D16" s="16"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
@@ -3029,11 +3119,11 @@
       <c r="D17" s="16"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
@@ -3045,11 +3135,11 @@
       <c r="D18" s="16"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="6"/>
@@ -3061,11 +3151,11 @@
       <c r="D19" s="16"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
       <c r="N19" s="6"/>
@@ -3077,11 +3167,11 @@
       <c r="D20" s="16"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="6"/>
@@ -3093,11 +3183,11 @@
       <c r="D21" s="16"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="6"/>
@@ -3109,11 +3199,11 @@
       <c r="D22" s="16"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="6"/>
@@ -3125,11 +3215,11 @@
       <c r="D23" s="16"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="6"/>
@@ -3345,13 +3435,13 @@
       <c r="G8" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="31" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="31" t="s">
         <v>230</v>
       </c>
       <c r="K8" s="13"/>
@@ -3385,11 +3475,11 @@
       <c r="G9" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="32"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
@@ -3421,11 +3511,11 @@
       <c r="G10" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="J10" s="28"/>
+      <c r="J10" s="32"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
@@ -3457,11 +3547,11 @@
       <c r="G11" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="J11" s="28"/>
+      <c r="J11" s="32"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
@@ -3493,11 +3583,11 @@
       <c r="G12" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="32"/>
       <c r="I12" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="J12" s="28"/>
+      <c r="J12" s="32"/>
       <c r="K12" s="13"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
@@ -3529,11 +3619,11 @@
       <c r="G13" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="J13" s="28"/>
+      <c r="J13" s="32"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
@@ -3565,11 +3655,11 @@
       <c r="G14" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="32"/>
       <c r="I14" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="J14" s="28"/>
+      <c r="J14" s="32"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>62</v>
@@ -3601,11 +3691,11 @@
       <c r="G15" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="32"/>
       <c r="I15" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="J15" s="28"/>
+      <c r="J15" s="32"/>
       <c r="K15" s="13"/>
       <c r="L15" s="15" t="s">
         <v>62</v>
@@ -3622,11 +3712,11 @@
       <c r="D16" s="16"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="31"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="6"/>
@@ -3638,11 +3728,11 @@
       <c r="D17" s="16"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="31"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="28"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="6"/>
@@ -3654,11 +3744,11 @@
       <c r="D18" s="16"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="31"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="28"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="6"/>
@@ -3670,11 +3760,11 @@
       <c r="D19" s="16"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="31"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="28"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
       <c r="N19" s="6"/>
@@ -3696,7 +3786,7 @@
   <sheetPr>
     <tabColor rgb="FF7F6000"/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3827,8 +3917,12 @@
       <c r="F6" s="15">
         <v>99</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="G6" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="16" t="s">
@@ -3861,10 +3955,16 @@
       <c r="F7" s="15">
         <v>99</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="G7" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
+      <c r="J7" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K7" s="16" t="s">
         <v>65</v>
       </c>
@@ -3895,10 +3995,16 @@
       <c r="F8" s="15">
         <v>99</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+      <c r="J8" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K8" s="16" t="s">
         <v>135</v>
       </c>
@@ -3931,10 +4037,16 @@
       <c r="F9" s="15">
         <v>99</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K9" s="16" t="s">
         <v>139</v>
       </c>
@@ -3967,10 +4079,16 @@
       <c r="F10" s="15">
         <v>99</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="G10" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
+      <c r="J10" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K10" s="16" t="s">
         <v>61</v>
       </c>
@@ -4001,10 +4119,16 @@
       <c r="F11" s="15">
         <v>99</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
+      <c r="G11" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
+      <c r="J11" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K11" s="16" t="s">
         <v>65</v>
       </c>
@@ -4035,10 +4159,16 @@
       <c r="F12" s="15">
         <v>99</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
+      <c r="G12" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
+      <c r="J12" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K12" s="16" t="s">
         <v>146</v>
       </c>
@@ -4069,10 +4199,16 @@
       <c r="F13" s="15">
         <v>99</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
+      <c r="G13" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="J13" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K13" s="16" t="s">
         <v>152</v>
       </c>
@@ -4103,10 +4239,16 @@
       <c r="F14" s="15">
         <v>99</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
+      <c r="G14" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
+      <c r="J14" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K14" s="16" t="s">
         <v>61</v>
       </c>
@@ -4137,10 +4279,16 @@
       <c r="F15" s="15">
         <v>99</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
+      <c r="G15" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
+      <c r="J15" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K15" s="16" t="s">
         <v>65</v>
       </c>
@@ -4171,10 +4319,16 @@
       <c r="F16" s="15">
         <v>99</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="G16" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
+      <c r="J16" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K16" s="16" t="s">
         <v>154</v>
       </c>
@@ -4186,7 +4340,7 @@
       </c>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15">
         <v>13</v>
       </c>
@@ -4205,10 +4359,16 @@
       <c r="F17" s="15">
         <v>99</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K17" s="16" t="s">
         <v>158</v>
       </c>
@@ -4220,7 +4380,7 @@
       </c>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
         <v>14</v>
       </c>
@@ -4239,10 +4399,16 @@
       <c r="F18" s="15">
         <v>99</v>
       </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="G18" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K18" s="16" t="s">
         <v>146</v>
       </c>
@@ -4254,7 +4420,7 @@
       </c>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
         <v>15</v>
       </c>
@@ -4273,10 +4439,16 @@
       <c r="F19" s="15">
         <v>99</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K19" s="16" t="s">
         <v>69</v>
       </c>
@@ -4288,7 +4460,7 @@
       </c>
       <c r="N19" s="16"/>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15">
         <v>16</v>
       </c>
@@ -4307,10 +4479,16 @@
       <c r="F20" s="15">
         <v>99</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="G20" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K20" s="16" t="s">
         <v>150</v>
       </c>
@@ -4322,7 +4500,7 @@
       </c>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15">
         <v>17</v>
       </c>
@@ -4341,10 +4519,16 @@
       <c r="F21" s="15">
         <v>99</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K21" s="16" t="s">
         <v>146</v>
       </c>
@@ -4356,7 +4540,7 @@
       </c>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="15">
         <v>18</v>
       </c>
@@ -4375,10 +4559,16 @@
       <c r="F22" s="15">
         <v>99</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="G22" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K22" s="16" t="s">
         <v>150</v>
       </c>
@@ -4390,7 +4580,7 @@
       </c>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="15">
         <v>19</v>
       </c>
@@ -4409,10 +4599,16 @@
       <c r="F23" s="15">
         <v>99</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K23" s="16" t="s">
         <v>154</v>
       </c>
@@ -4424,7 +4620,7 @@
       </c>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15">
         <v>20</v>
       </c>
@@ -4443,10 +4639,16 @@
       <c r="F24" s="15">
         <v>99</v>
       </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="G24" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
+      <c r="J24" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K24" s="16" t="s">
         <v>156</v>
       </c>
@@ -4458,7 +4660,7 @@
       </c>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15">
         <v>21</v>
       </c>
@@ -4477,10 +4679,16 @@
       <c r="F25" s="15">
         <v>99</v>
       </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="G25" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
+      <c r="J25" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K25" s="16" t="s">
         <v>154</v>
       </c>
@@ -4492,7 +4700,7 @@
       </c>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="15">
         <v>22</v>
       </c>
@@ -4511,10 +4719,16 @@
       <c r="F26" s="15">
         <v>99</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="G26" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
+      <c r="J26" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K26" s="16" t="s">
         <v>88</v>
       </c>
@@ -4526,7 +4740,7 @@
       </c>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15">
         <v>23</v>
       </c>
@@ -4545,10 +4759,16 @@
       <c r="F27" s="15">
         <v>99</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="G27" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
+      <c r="J27" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="K27" s="16" t="s">
         <v>156</v>
       </c>
@@ -4560,43 +4780,47 @@
       </c>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="15">
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="34">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="34">
         <v>99</v>
       </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="16" t="s">
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="L28" s="16" t="s">
+      <c r="L28" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="M28" s="15" t="s">
+      <c r="M28" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="N28" s="16" t="s">
+      <c r="N28" s="35" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O28" s="26"/>
+      <c r="P28" s="37" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="15"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -4612,7 +4836,7 @@
       <c r="M29" s="15"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -4628,7 +4852,7 @@
       <c r="M30" s="15"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -4644,7 +4868,7 @@
       <c r="M31" s="15"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -4726,6 +4950,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:N36" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32DDD1E-A823-4633-A374-666D93303B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112AA8E8-45CB-40A7-AD5F-50EE2B271228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="803" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="312">
   <si>
     <t>Network Addressing Plan - VLAN Summary</t>
   </si>
@@ -968,6 +968,21 @@
   </si>
   <si>
     <t>NO IP, BUT BOTH THE DEVICES CONNECTED ARE ON VLAN 10</t>
+  </si>
+  <si>
+    <t>Admin PC</t>
+  </si>
+  <si>
+    <t>192.168.99.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch 14 </t>
+  </si>
+  <si>
+    <t>ADMIN PC - for vlan 99 MNGT.</t>
+  </si>
+  <si>
+    <t>End-Device</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1053,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1102,6 +1117,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
@@ -1179,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1261,15 +1282,6 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1281,6 +1293,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1751,7 +1778,7 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="5">
         <f>COUNTA('VLAN 99 - Management'!B5:B80)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>31</v>
@@ -2021,13 +2048,13 @@
       <c r="G8" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="35" t="s">
         <v>225</v>
       </c>
       <c r="K8" s="13"/>
@@ -2061,11 +2088,11 @@
       <c r="G9" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="J9" s="32"/>
+      <c r="J9" s="36"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>57</v>
@@ -2097,11 +2124,11 @@
       <c r="G10" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="J10" s="32"/>
+      <c r="J10" s="36"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>57</v>
@@ -2133,11 +2160,11 @@
       <c r="G11" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="J11" s="32"/>
+      <c r="J11" s="36"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>57</v>
@@ -2169,11 +2196,11 @@
       <c r="G12" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="J12" s="32"/>
+      <c r="J12" s="36"/>
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="s">
         <v>57</v>
@@ -2205,11 +2232,11 @@
       <c r="G13" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="J13" s="32"/>
+      <c r="J13" s="36"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>57</v>
@@ -2241,11 +2268,11 @@
       <c r="G14" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="J14" s="32"/>
+      <c r="J14" s="36"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>57</v>
@@ -2277,11 +2304,11 @@
       <c r="G15" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="J15" s="32"/>
+      <c r="J15" s="36"/>
       <c r="K15" s="13"/>
       <c r="L15" s="15" t="s">
         <v>57</v>
@@ -2313,11 +2340,11 @@
       <c r="G16" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="J16" s="32"/>
+      <c r="J16" s="36"/>
       <c r="K16" s="13"/>
       <c r="L16" s="15" t="s">
         <v>57</v>
@@ -2349,11 +2376,11 @@
       <c r="G17" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="J17" s="32"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="13"/>
       <c r="L17" s="15" t="s">
         <v>57</v>
@@ -2385,11 +2412,11 @@
       <c r="G18" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="J18" s="32"/>
+      <c r="J18" s="36"/>
       <c r="K18" s="13"/>
       <c r="L18" s="15" t="s">
         <v>57</v>
@@ -2421,11 +2448,11 @@
       <c r="G19" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="J19" s="32"/>
+      <c r="J19" s="36"/>
       <c r="K19" s="13"/>
       <c r="L19" s="15" t="s">
         <v>57</v>
@@ -2459,11 +2486,11 @@
       <c r="G20" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="33"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="J20" s="33"/>
+      <c r="J20" s="37"/>
       <c r="K20" s="13"/>
       <c r="L20" s="15" t="s">
         <v>57</v>
@@ -2846,13 +2873,13 @@
       <c r="G8" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="35" t="s">
         <v>247</v>
       </c>
       <c r="K8" s="13"/>
@@ -2886,11 +2913,11 @@
       <c r="G9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="J9" s="32"/>
+      <c r="J9" s="36"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
@@ -2922,11 +2949,11 @@
       <c r="G10" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="J10" s="32"/>
+      <c r="J10" s="36"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
@@ -2958,11 +2985,11 @@
       <c r="G11" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="J11" s="32"/>
+      <c r="J11" s="36"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
@@ -2994,11 +3021,11 @@
       <c r="G12" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="J12" s="32"/>
+      <c r="J12" s="36"/>
       <c r="K12" s="13"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
@@ -3030,11 +3057,11 @@
       <c r="G13" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="J13" s="32"/>
+      <c r="J13" s="36"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
@@ -3066,11 +3093,11 @@
       <c r="G14" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="H14" s="33"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="J14" s="33"/>
+      <c r="J14" s="37"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>62</v>
@@ -3435,13 +3462,13 @@
       <c r="G8" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="35" t="s">
         <v>230</v>
       </c>
       <c r="K8" s="13"/>
@@ -3475,11 +3502,11 @@
       <c r="G9" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="J9" s="32"/>
+      <c r="J9" s="36"/>
       <c r="K9" s="13"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
@@ -3511,11 +3538,11 @@
       <c r="G10" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="J10" s="32"/>
+      <c r="J10" s="36"/>
       <c r="K10" s="13"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
@@ -3547,11 +3574,11 @@
       <c r="G11" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="J11" s="32"/>
+      <c r="J11" s="36"/>
       <c r="K11" s="13"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
@@ -3583,11 +3610,11 @@
       <c r="G12" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="J12" s="32"/>
+      <c r="J12" s="36"/>
       <c r="K12" s="13"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
@@ -3619,11 +3646,11 @@
       <c r="G13" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="J13" s="32"/>
+      <c r="J13" s="36"/>
       <c r="K13" s="13"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
@@ -3655,11 +3682,11 @@
       <c r="G14" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="J14" s="32"/>
+      <c r="J14" s="36"/>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
         <v>62</v>
@@ -3691,11 +3718,11 @@
       <c r="G15" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="J15" s="32"/>
+      <c r="J15" s="36"/>
       <c r="K15" s="13"/>
       <c r="L15" s="15" t="s">
         <v>62</v>
@@ -4781,60 +4808,86 @@
       <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="34">
+      <c r="A28" s="31">
         <v>24</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="31">
         <v>99</v>
       </c>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="35" t="s">
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="L28" s="35" t="s">
+      <c r="L28" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="N28" s="35" t="s">
+      <c r="N28" s="32" t="s">
         <v>166</v>
       </c>
       <c r="O28" s="26"/>
-      <c r="P28" s="37" t="s">
+      <c r="P28" s="34" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="16"/>
+      <c r="A29" s="27">
+        <v>25</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="F29" s="27">
+        <v>99</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="L29" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="M29" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="N29" s="38" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15"/>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C0BC46-957A-4578-9432-12C025770DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FDA83B-ED6D-4EB4-9E1F-AB624EB97E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="751" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="751" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN Summary" sheetId="1" r:id="rId1"/>
@@ -922,9 +922,6 @@
     <t>Permit host 192.168.99.50 only</t>
   </si>
   <si>
-    <t>Use the CORE-1 password you already set</t>
-  </si>
-  <si>
     <t>labadmin</t>
   </si>
   <si>
@@ -1232,13 +1229,27 @@
   </si>
   <si>
     <t>NetAdmin@2026!</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enable Password is : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CoreEnable@2026!</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1305,8 +1316,19 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1347,6 +1369,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1411,11 +1439,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1446,9 +1471,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1511,6 +1533,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1799,253 +1830,253 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="7">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="6">
         <f>COUNTA('VLAN 10 - End Devices'!B5:B71)</f>
         <v>16</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="R5" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>20</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="7">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="6">
         <f>COUNTA('VLAN 20 - Servers'!B5:B80)</f>
         <v>10</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>30</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="7">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="6">
         <f>COUNTA('VLAN 30 - Security'!B5:B80)</f>
         <v>11</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="R7" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>99</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="7">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="6">
         <f>COUNTA('VLAN 99 - Management'!B5:B80)</f>
         <v>48</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="R8" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>100</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="7">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="6">
         <f>COUNTA('VLAN 100 - FW-NAT'!B5:B80)</f>
         <v>11</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="R9" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2076,795 +2107,795 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>10</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="13" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="16" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="14" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>10</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="13" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="16" t="s">
+      <c r="M6" s="12"/>
+      <c r="N6" s="14" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>10</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="16" t="s">
+      <c r="M7" s="12"/>
+      <c r="N7" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+      <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <v>10</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="N8" s="8"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+      <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <v>10</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="15" t="s">
+      <c r="H9" s="36"/>
+      <c r="I9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="17" t="s">
+      <c r="J9" s="36"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="N9" s="8"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>10</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="15" t="s">
+      <c r="H10" s="36"/>
+      <c r="I10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17" t="s">
+      <c r="J10" s="36"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="N10" s="8"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+      <c r="A11" s="15">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>10</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="15" t="s">
+      <c r="H11" s="36"/>
+      <c r="I11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="17" t="s">
+      <c r="J11" s="36"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="N11" s="8"/>
-    </row>
-    <row r="12" spans="1:14" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="21">
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
         <v>13</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="19">
         <v>10</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="21" t="s">
+      <c r="H12" s="36"/>
+      <c r="I12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21" t="s">
+      <c r="J12" s="36"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="23" t="s">
+      <c r="M12" s="19"/>
+      <c r="N12" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
+      <c r="A13" s="15">
         <v>15</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>10</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="36"/>
+      <c r="I13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="17" t="s">
+      <c r="J13" s="36"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="N13" s="8"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="17">
+      <c r="A14" s="15">
         <v>17</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>10</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="15" t="s">
+      <c r="H14" s="36"/>
+      <c r="I14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="17" t="s">
+      <c r="J14" s="36"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="N14" s="8"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="17">
+      <c r="A15" s="15">
         <v>18</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <v>10</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="15" t="s">
+      <c r="H15" s="36"/>
+      <c r="I15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="17" t="s">
+      <c r="J15" s="36"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="N15" s="8"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17">
+      <c r="A16" s="15">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="15">
         <v>10</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="15" t="s">
+      <c r="H16" s="36"/>
+      <c r="I16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="17" t="s">
+      <c r="J16" s="36"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="19" t="s">
+      <c r="M16" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="N16" s="8"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="17">
+      <c r="A17" s="15">
         <v>20</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <v>10</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="15" t="s">
+      <c r="H17" s="36"/>
+      <c r="I17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="17" t="s">
+      <c r="J17" s="36"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="N17" s="8"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17">
+      <c r="A18" s="15">
         <v>22</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="15">
         <v>10</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="15" t="s">
+      <c r="H18" s="36"/>
+      <c r="I18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="17" t="s">
+      <c r="J18" s="36"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="N18" s="8"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
+      <c r="A19" s="15">
         <v>24</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="15">
         <v>10</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="15" t="s">
+      <c r="H19" s="36"/>
+      <c r="I19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="17" t="s">
+      <c r="J19" s="36"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="N19" s="25" t="s">
+      <c r="N19" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="17">
+      <c r="A20" s="15">
         <v>25</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="15">
         <v>10</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="15" t="s">
+      <c r="H20" s="36"/>
+      <c r="I20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="17" t="s">
+      <c r="J20" s="36"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="N20" s="25" t="s">
+      <c r="N20" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="8"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="17"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="8"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="8"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="7"/>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="17"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="8"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="7"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="17"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="8"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="17"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="8"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="7"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="17"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="8"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="7"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="17"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="8"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="7"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="17"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="8"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="17"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="8"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:A20" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -2900,559 +2931,559 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>20</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="13" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="16" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="14" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>20</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="13" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="16" t="s">
+      <c r="M6" s="12"/>
+      <c r="N6" s="14" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>20</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="16" t="s">
+      <c r="M7" s="12"/>
+      <c r="N7" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+      <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <v>20</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="N8" s="8"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+      <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <v>20</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="15" t="s">
+      <c r="H9" s="36"/>
+      <c r="I9" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="17" t="s">
+      <c r="J9" s="36"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="N9" s="8"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>20</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="15" t="s">
+      <c r="H10" s="36"/>
+      <c r="I10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17" t="s">
+      <c r="J10" s="36"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="N10" s="8"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+      <c r="A11" s="15">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>20</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="15" t="s">
+      <c r="H11" s="36"/>
+      <c r="I11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="17" t="s">
+      <c r="J11" s="36"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="N11" s="8"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17">
+      <c r="A12" s="15">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <v>20</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="15" t="s">
+      <c r="H12" s="36"/>
+      <c r="I12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17" t="s">
+      <c r="J12" s="36"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="N12" s="8"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
+      <c r="A13" s="15">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>20</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="36"/>
+      <c r="I13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="17" t="s">
+      <c r="J13" s="36"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="N13" s="8"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="17">
+      <c r="A14" s="15">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>20</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="15" t="s">
+      <c r="H14" s="36"/>
+      <c r="I14" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="17" t="s">
+      <c r="J14" s="36"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="N14" s="8"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="8"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="8"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="8"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="8"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="8"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="7"/>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="8"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="7"/>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="8"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="7"/>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="17"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="8"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="8"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N23" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -3488,515 +3519,515 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>30</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="13" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="16" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="14" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>30</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="13" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="16" t="s">
+      <c r="M6" s="12"/>
+      <c r="N6" s="14" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>30</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="16" t="s">
+      <c r="M7" s="12"/>
+      <c r="N7" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+      <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <v>30</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="N8" s="8"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+      <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <v>30</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="15" t="s">
+      <c r="H9" s="37"/>
+      <c r="I9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="17" t="s">
+      <c r="J9" s="37"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="N9" s="8"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>30</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="15" t="s">
+      <c r="H10" s="37"/>
+      <c r="I10" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17" t="s">
+      <c r="J10" s="37"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="N10" s="8"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+      <c r="A11" s="15">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>30</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="15" t="s">
+      <c r="H11" s="37"/>
+      <c r="I11" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="17" t="s">
+      <c r="J11" s="37"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="N11" s="8"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17">
+      <c r="A12" s="15">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <v>30</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="15" t="s">
+      <c r="H12" s="37"/>
+      <c r="I12" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17" t="s">
+      <c r="J12" s="37"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="N12" s="8"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
+      <c r="A13" s="15">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>30</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="37"/>
+      <c r="I13" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="17" t="s">
+      <c r="J13" s="37"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="N13" s="8"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="17">
+      <c r="A14" s="15">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>30</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="15" t="s">
+      <c r="H14" s="37"/>
+      <c r="I14" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="17" t="s">
+      <c r="J14" s="37"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="N14" s="8"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="17">
+      <c r="A15" s="15">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <v>30</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="15" t="s">
+      <c r="H15" s="37"/>
+      <c r="I15" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="17" t="s">
+      <c r="J15" s="37"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="N15" s="8"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="8"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="8"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="8"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="8"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N19" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -4032,2109 +4063,2109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>99</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="14" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="13" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17">
+      <c r="A6" s="15">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="15">
         <v>99</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="18" t="s">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17">
+      <c r="A7" s="15">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="15">
         <v>99</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15" t="s">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+      <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <v>99</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15" t="s">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="N8" s="16" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+      <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <v>99</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15" t="s">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="16" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>99</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15" t="s">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+      <c r="A11" s="15">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>99</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15" t="s">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17">
+      <c r="A12" s="15">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <v>99</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15" t="s">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L12" s="18" t="s">
+      <c r="L12" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
+      <c r="A13" s="15">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>99</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15" t="s">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="17">
+      <c r="A14" s="15">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>99</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15" t="s">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="M14" s="17" t="s">
+      <c r="M14" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N14" s="18"/>
+      <c r="N14" s="16"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="17">
+      <c r="A15" s="15">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <v>99</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15" t="s">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="18" t="s">
+      <c r="L15" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="M15" s="17" t="s">
+      <c r="M15" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N15" s="18"/>
+      <c r="N15" s="16"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17">
+      <c r="A16" s="15">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="15">
         <v>99</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15" t="s">
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="L16" s="18" t="s">
+      <c r="L16" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="M16" s="17" t="s">
+      <c r="M16" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N16" s="18"/>
+      <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="17">
+      <c r="A17" s="15">
         <v>13</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <v>99</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15" t="s">
+      <c r="I17" s="1"/>
+      <c r="J17" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="L17" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="M17" s="17" t="s">
+      <c r="M17" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N17" s="18"/>
+      <c r="N17" s="16"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17">
+      <c r="A18" s="15">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="15">
         <v>99</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15" t="s">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L18" s="18" t="s">
+      <c r="L18" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="M18" s="17" t="s">
+      <c r="M18" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N18" s="18"/>
+      <c r="N18" s="16"/>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
+      <c r="A19" s="15">
         <v>15</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="15">
         <v>99</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15" t="s">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="L19" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="M19" s="17" t="s">
+      <c r="M19" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N19" s="18"/>
+      <c r="N19" s="16"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="17">
+      <c r="A20" s="15">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="15">
         <v>99</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15" t="s">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="L20" s="18" t="s">
+      <c r="L20" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="M20" s="17" t="s">
+      <c r="M20" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N20" s="18"/>
+      <c r="N20" s="16"/>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17">
+      <c r="A21" s="15">
         <v>17</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="15">
         <v>99</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15" t="s">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L21" s="18" t="s">
+      <c r="L21" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="M21" s="17" t="s">
+      <c r="M21" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N21" s="18"/>
+      <c r="N21" s="16"/>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="17">
+      <c r="A22" s="15">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="15">
         <v>99</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15" t="s">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="K22" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="L22" s="18" t="s">
+      <c r="L22" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="M22" s="17" t="s">
+      <c r="M22" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N22" s="18"/>
+      <c r="N22" s="16"/>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="17">
+      <c r="A23" s="15">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="15">
         <v>99</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="H23" s="15" t="s">
+      <c r="H23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15" t="s">
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K23" s="18" t="s">
+      <c r="K23" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="L23" s="18" t="s">
+      <c r="L23" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M23" s="17" t="s">
+      <c r="M23" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N23" s="18"/>
+      <c r="N23" s="16"/>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="17">
+      <c r="A24" s="15">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="15">
         <v>99</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15" t="s">
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K24" s="18" t="s">
+      <c r="K24" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="L24" s="18" t="s">
+      <c r="L24" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="M24" s="17" t="s">
+      <c r="M24" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N24" s="18"/>
+      <c r="N24" s="16"/>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="17">
+      <c r="A25" s="15">
         <v>21</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="15">
         <v>99</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15" t="s">
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="K25" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="L25" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="M25" s="17" t="s">
+      <c r="M25" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N25" s="18"/>
+      <c r="N25" s="16"/>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="17">
+      <c r="A26" s="15">
         <v>22</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="15">
         <v>99</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15" t="s">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="K26" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="L26" s="18" t="s">
+      <c r="L26" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="M26" s="17" t="s">
+      <c r="M26" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N26" s="18"/>
+      <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="17">
+      <c r="A27" s="15">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="15">
         <v>99</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="H27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15" t="s">
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K27" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="L27" s="18" t="s">
+      <c r="L27" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="M27" s="17" t="s">
+      <c r="M27" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="N27" s="18"/>
+      <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="29">
+      <c r="A28" s="27">
         <v>24</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="27">
         <v>99</v>
       </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="30" t="s">
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="L28" s="30" t="s">
+      <c r="L28" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="N28" s="30" t="s">
+      <c r="N28" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="O28" s="24"/>
-      <c r="P28" s="32" t="s">
+      <c r="O28" s="22"/>
+      <c r="P28" s="30" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="19">
+      <c r="A29" s="17">
         <v>25</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="17">
         <v>99</v>
       </c>
-      <c r="G29" s="34" t="s">
+      <c r="G29" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="H29" s="34" t="s">
+      <c r="H29" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34" t="s">
+      <c r="I29" s="32"/>
+      <c r="J29" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="K29" s="33" t="s">
+      <c r="K29" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="L29" s="33" t="s">
+      <c r="L29" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="M29" s="19" t="s">
+      <c r="M29" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="N29" s="33" t="s">
+      <c r="N29" s="31" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="17"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="18"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="16"/>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="17"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="18"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="16"/>
     </row>
     <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="17"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="18"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="16"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="18"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="16"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="18"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="16"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="17"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="18"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="16"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="17"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="18"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="16"/>
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K41" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="L41" s="5" t="s">
+      <c r="L41" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="M41" s="35"/>
-      <c r="N41" s="5" t="s">
+      <c r="M41" s="33"/>
+      <c r="N41" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="17">
+      <c r="A42" s="15">
         <v>1</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="E42" s="36" t="s">
+      <c r="E42" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G42" s="37" t="s">
+      <c r="G42" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="M42" s="33"/>
+      <c r="N42" s="38" t="s">
         <v>394</v>
       </c>
-      <c r="H42" s="36" t="s">
+    </row>
+    <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="15">
+        <v>2</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H43" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I42" s="17" t="s">
+      <c r="I43" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J42" s="17" t="s">
+      <c r="J43" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K42" s="17" t="s">
+      <c r="K43" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L42" s="8" t="s">
+      <c r="L43" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M42" s="35"/>
-      <c r="N42" s="18" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="17">
-        <v>2</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="F43" s="17" t="s">
+      <c r="M43" s="33"/>
+      <c r="N43" s="16"/>
+    </row>
+    <row r="44" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="15">
+        <v>3</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="F44" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G43" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="H43" s="36" t="s">
+      <c r="G44" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="H44" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="17" t="s">
+      <c r="I44" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J43" s="17" t="s">
+      <c r="J44" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K43" s="17" t="s">
+      <c r="K44" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L43" s="8" t="s">
+      <c r="L44" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M43" s="35"/>
-      <c r="N43" s="18"/>
-    </row>
-    <row r="44" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="17">
-        <v>3</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="F44" s="17" t="s">
+      <c r="M44" s="33"/>
+      <c r="N44" s="16"/>
+    </row>
+    <row r="45" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="15">
+        <v>4</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="F45" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="H44" s="36" t="s">
+      <c r="G45" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H45" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="I45" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J44" s="17" t="s">
+      <c r="J45" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K44" s="17" t="s">
+      <c r="K45" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L44" s="8" t="s">
+      <c r="L45" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M44" s="35"/>
-      <c r="N44" s="18"/>
-    </row>
-    <row r="45" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="17">
-        <v>4</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="E45" s="36" t="s">
-        <v>298</v>
-      </c>
-      <c r="F45" s="17" t="s">
+      <c r="M45" s="33"/>
+      <c r="N45" s="16"/>
+    </row>
+    <row r="46" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="15">
+        <v>5</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F46" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="H45" s="36" t="s">
+      <c r="G46" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="H46" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I45" s="17" t="s">
+      <c r="I46" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J45" s="17" t="s">
+      <c r="J46" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K45" s="17" t="s">
+      <c r="K46" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L45" s="8" t="s">
+      <c r="L46" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M45" s="35"/>
-      <c r="N45" s="18"/>
-    </row>
-    <row r="46" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="17">
-        <v>5</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>301</v>
-      </c>
-      <c r="F46" s="17" t="s">
+      <c r="M46" s="33"/>
+      <c r="N46" s="16"/>
+    </row>
+    <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="15">
+        <v>6</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="F47" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="H46" s="36" t="s">
+      <c r="G47" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="H47" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I46" s="17" t="s">
+      <c r="I47" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="J47" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K46" s="17" t="s">
+      <c r="K47" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L46" s="8" t="s">
+      <c r="L47" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M46" s="35"/>
-      <c r="N46" s="18"/>
-    </row>
-    <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="17">
-        <v>6</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="D47" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="F47" s="17" t="s">
+      <c r="M47" s="33"/>
+      <c r="N47" s="16"/>
+    </row>
+    <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="15">
+        <v>7</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="F48" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="H47" s="36" t="s">
+      <c r="G48" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H48" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I47" s="17" t="s">
+      <c r="I48" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J47" s="17" t="s">
+      <c r="J48" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K47" s="17" t="s">
+      <c r="K48" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L47" s="8" t="s">
+      <c r="L48" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M47" s="35"/>
-      <c r="N47" s="18"/>
-    </row>
-    <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="17">
-        <v>7</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="D48" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="F48" s="17" t="s">
+      <c r="M48" s="33"/>
+      <c r="N48" s="16"/>
+    </row>
+    <row r="49" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="15">
+        <v>8</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="E49" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="F49" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="H48" s="36" t="s">
+      <c r="G49" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="H49" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="I49" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J48" s="17" t="s">
+      <c r="J49" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K48" s="17" t="s">
+      <c r="K49" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L48" s="8" t="s">
+      <c r="L49" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M48" s="35"/>
-      <c r="N48" s="18"/>
-    </row>
-    <row r="49" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="17">
-        <v>8</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="D49" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="F49" s="17" t="s">
+      <c r="M49" s="33"/>
+      <c r="N49" s="16"/>
+    </row>
+    <row r="50" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="15">
+        <v>9</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="F50" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G49" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="H49" s="36" t="s">
+      <c r="G50" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="H50" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="I50" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J49" s="17" t="s">
+      <c r="J50" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K49" s="17" t="s">
+      <c r="K50" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L49" s="8" t="s">
+      <c r="L50" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M49" s="35"/>
-      <c r="N49" s="18"/>
-    </row>
-    <row r="50" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="17">
-        <v>9</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="D50" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="F50" s="17" t="s">
+      <c r="M50" s="33"/>
+      <c r="N50" s="16"/>
+    </row>
+    <row r="51" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="15">
+        <v>10</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E51" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="F51" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H50" s="36" t="s">
+      <c r="G51" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H51" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I50" s="17" t="s">
+      <c r="I51" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J50" s="17" t="s">
+      <c r="J51" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K50" s="17" t="s">
+      <c r="K51" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L50" s="8" t="s">
+      <c r="L51" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M50" s="35"/>
-      <c r="N50" s="18"/>
-    </row>
-    <row r="51" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="17">
-        <v>10</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="F51" s="17" t="s">
+      <c r="M51" s="33"/>
+      <c r="N51" s="16"/>
+    </row>
+    <row r="52" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="15">
+        <v>11</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="F52" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="H51" s="36" t="s">
+      <c r="G52" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H52" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I52" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J51" s="17" t="s">
+      <c r="J52" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K51" s="17" t="s">
+      <c r="K52" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L51" s="8" t="s">
+      <c r="L52" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M51" s="35"/>
-      <c r="N51" s="18"/>
-    </row>
-    <row r="52" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="17">
-        <v>11</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="D52" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>319</v>
-      </c>
-      <c r="F52" s="17" t="s">
+      <c r="M52" s="33"/>
+      <c r="N52" s="16"/>
+    </row>
+    <row r="53" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="15">
+        <v>12</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="F53" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="H52" s="36" t="s">
+      <c r="G53" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H53" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I53" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J52" s="17" t="s">
+      <c r="J53" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K52" s="17" t="s">
+      <c r="K53" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L52" s="8" t="s">
+      <c r="L53" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M52" s="35"/>
-      <c r="N52" s="18"/>
-    </row>
-    <row r="53" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="17">
-        <v>12</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>322</v>
-      </c>
-      <c r="F53" s="17" t="s">
+      <c r="M53" s="33"/>
+      <c r="N53" s="16"/>
+    </row>
+    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="15">
+        <v>13</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="F54" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H53" s="36" t="s">
+      <c r="G54" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H54" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I54" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J53" s="17" t="s">
+      <c r="J54" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K53" s="17" t="s">
+      <c r="K54" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L53" s="8" t="s">
+      <c r="L54" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M53" s="35"/>
-      <c r="N53" s="18"/>
-    </row>
-    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="17">
-        <v>13</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="F54" s="17" t="s">
+      <c r="M54" s="33"/>
+      <c r="N54" s="16"/>
+    </row>
+    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="15">
+        <v>14</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="F55" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H54" s="36" t="s">
+      <c r="G55" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H55" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I54" s="17" t="s">
+      <c r="I55" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J54" s="17" t="s">
+      <c r="J55" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K54" s="17" t="s">
+      <c r="K55" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L54" s="8" t="s">
+      <c r="L55" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M54" s="35"/>
-      <c r="N54" s="18"/>
-    </row>
-    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="17">
-        <v>14</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D55" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="F55" s="17" t="s">
+      <c r="M55" s="33"/>
+      <c r="N55" s="16"/>
+    </row>
+    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="15">
+        <v>15</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="F56" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="H55" s="36" t="s">
+      <c r="G56" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H56" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I55" s="17" t="s">
+      <c r="I56" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J55" s="17" t="s">
+      <c r="J56" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K55" s="17" t="s">
+      <c r="K56" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L55" s="8" t="s">
+      <c r="L56" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M55" s="35"/>
-      <c r="N55" s="18"/>
-    </row>
-    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="17">
-        <v>15</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="F56" s="17" t="s">
+      <c r="M56" s="33"/>
+      <c r="N56" s="16"/>
+    </row>
+    <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="15">
+        <v>16</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="F57" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="H56" s="36" t="s">
+      <c r="G57" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H57" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I56" s="17" t="s">
+      <c r="I57" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J56" s="17" t="s">
+      <c r="J57" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K56" s="17" t="s">
+      <c r="K57" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="L57" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M56" s="35"/>
-      <c r="N56" s="18"/>
-    </row>
-    <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="17">
-        <v>16</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="F57" s="17" t="s">
+      <c r="M57" s="33"/>
+      <c r="N57" s="16"/>
+    </row>
+    <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="15">
+        <v>17</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="F58" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="H57" s="36" t="s">
+      <c r="G58" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H58" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I57" s="17" t="s">
+      <c r="I58" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J57" s="17" t="s">
+      <c r="J58" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K57" s="17" t="s">
+      <c r="K58" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L57" s="8" t="s">
+      <c r="L58" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M57" s="35"/>
-      <c r="N57" s="18"/>
-    </row>
-    <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="17">
-        <v>17</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>337</v>
-      </c>
-      <c r="F58" s="17" t="s">
+      <c r="M58" s="33"/>
+      <c r="N58" s="16"/>
+    </row>
+    <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="15">
+        <v>18</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="F59" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="H58" s="36" t="s">
+      <c r="G59" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="H59" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I58" s="17" t="s">
+      <c r="I59" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J58" s="17" t="s">
+      <c r="J59" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K58" s="17" t="s">
+      <c r="K59" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L59" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M58" s="35"/>
-      <c r="N58" s="18"/>
-    </row>
-    <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="17">
-        <v>18</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D59" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>340</v>
-      </c>
-      <c r="F59" s="17" t="s">
+      <c r="M59" s="33"/>
+      <c r="N59" s="16"/>
+    </row>
+    <row r="60" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="15">
+        <v>19</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="H59" s="36" t="s">
+      <c r="G60" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="H60" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I59" s="17" t="s">
+      <c r="I60" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J59" s="17" t="s">
+      <c r="J60" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K59" s="17" t="s">
+      <c r="K60" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L59" s="8" t="s">
+      <c r="L60" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M59" s="35"/>
-      <c r="N59" s="18"/>
-    </row>
-    <row r="60" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="17">
-        <v>19</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="E60" s="36" t="s">
-        <v>343</v>
-      </c>
-      <c r="F60" s="17" t="s">
+      <c r="M60" s="33"/>
+      <c r="N60" s="16"/>
+    </row>
+    <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="15">
+        <v>20</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="F61" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="H60" s="36" t="s">
+      <c r="G61" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H61" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I60" s="17" t="s">
+      <c r="I61" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J60" s="17" t="s">
+      <c r="J61" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K60" s="17" t="s">
+      <c r="K61" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L60" s="8" t="s">
+      <c r="L61" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M60" s="35"/>
-      <c r="N60" s="18"/>
-    </row>
-    <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="17">
-        <v>20</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D61" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>346</v>
-      </c>
-      <c r="F61" s="17" t="s">
+      <c r="M61" s="33"/>
+      <c r="N61" s="16"/>
+    </row>
+    <row r="62" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="15">
+        <v>21</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="F62" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H61" s="36" t="s">
+      <c r="G62" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H62" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I61" s="17" t="s">
+      <c r="I62" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="17" t="s">
+      <c r="J62" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K61" s="17" t="s">
+      <c r="K62" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L61" s="8" t="s">
+      <c r="L62" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M61" s="35"/>
-      <c r="N61" s="18"/>
-    </row>
-    <row r="62" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="17">
-        <v>21</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D62" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>349</v>
-      </c>
-      <c r="F62" s="17" t="s">
+      <c r="M62" s="33"/>
+      <c r="N62" s="16"/>
+    </row>
+    <row r="63" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="15">
+        <v>22</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="E63" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="F63" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="H62" s="36" t="s">
+      <c r="G63" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H63" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="I62" s="17" t="s">
+      <c r="I63" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="J62" s="17" t="s">
+      <c r="J63" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="K62" s="17" t="s">
+      <c r="K63" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="L62" s="8" t="s">
+      <c r="L63" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M62" s="35"/>
-      <c r="N62" s="18"/>
-    </row>
-    <row r="63" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="17">
-        <v>22</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D63" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="E63" s="36" t="s">
-        <v>352</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="H63" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="I63" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="J63" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="K63" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="M63" s="35"/>
-      <c r="N63" s="18"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N36" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
@@ -6169,450 +6200,450 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="C5" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="12">
+        <v>100</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="12"/>
+      <c r="N5" s="14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="12">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="F6" s="12">
+        <v>100</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="14" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="F7" s="12">
+        <v>100</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15">
+        <v>4</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="F8" s="15">
+        <v>100</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="15">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="F9" s="15">
+        <v>100</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="B17" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="15">
+        <v>1</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="15">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="F5" s="13">
-        <v>100</v>
-      </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="16" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
-        <v>2</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="F6" s="13">
-        <v>100</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="16" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
+      <c r="B19" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="F7" s="13">
-        <v>100</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="16" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+      <c r="B20" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="F8" s="17">
-        <v>100</v>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+      <c r="B21" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="G21" s="17"/>
+      <c r="H21" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="F9" s="17">
-        <v>100</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="8"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="8"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="8"/>
-    </row>
-    <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17">
-        <v>1</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="B22" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
-        <v>2</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="17">
-        <v>3</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17">
-        <v>4</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="17">
-        <v>5</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="G22" s="17"/>
+      <c r="H22" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="18" t="s">
+      <c r="I22" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="I22" s="18" t="s">
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -1534,14 +1534,14 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2283,13 +2283,13 @@
       <c r="G8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="37" t="s">
         <v>72</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="37" t="s">
         <v>74</v>
       </c>
       <c r="K8" s="1"/>
@@ -2323,11 +2323,11 @@
       <c r="G9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="36"/>
+      <c r="J9" s="37"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
         <v>57</v>
@@ -2359,11 +2359,11 @@
       <c r="G10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J10" s="36"/>
+      <c r="J10" s="37"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
         <v>57</v>
@@ -2395,11 +2395,11 @@
       <c r="G11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="36"/>
+      <c r="J11" s="37"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
         <v>57</v>
@@ -2431,11 +2431,11 @@
       <c r="G12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="36"/>
+      <c r="J12" s="37"/>
       <c r="K12" s="19"/>
       <c r="L12" s="19" t="s">
         <v>57</v>
@@ -2467,11 +2467,11 @@
       <c r="G13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="36"/>
+      <c r="J13" s="37"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
         <v>57</v>
@@ -2503,11 +2503,11 @@
       <c r="G14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="36"/>
+      <c r="J14" s="37"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
         <v>57</v>
@@ -2539,11 +2539,11 @@
       <c r="G15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="36"/>
+      <c r="J15" s="37"/>
       <c r="K15" s="1"/>
       <c r="L15" s="15" t="s">
         <v>57</v>
@@ -2575,11 +2575,11 @@
       <c r="G16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="36"/>
+      <c r="J16" s="37"/>
       <c r="K16" s="1"/>
       <c r="L16" s="15" t="s">
         <v>57</v>
@@ -2611,11 +2611,11 @@
       <c r="G17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="36"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J17" s="36"/>
+      <c r="J17" s="37"/>
       <c r="K17" s="1"/>
       <c r="L17" s="15" t="s">
         <v>57</v>
@@ -2647,11 +2647,11 @@
       <c r="G18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="36"/>
+      <c r="J18" s="37"/>
       <c r="K18" s="1"/>
       <c r="L18" s="15" t="s">
         <v>57</v>
@@ -2683,11 +2683,11 @@
       <c r="G19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="37"/>
       <c r="I19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J19" s="36"/>
+      <c r="J19" s="37"/>
       <c r="K19" s="1"/>
       <c r="L19" s="15" t="s">
         <v>57</v>
@@ -2721,11 +2721,11 @@
       <c r="G20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="36"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J20" s="36"/>
+      <c r="J20" s="37"/>
       <c r="K20" s="1"/>
       <c r="L20" s="15" t="s">
         <v>57</v>
@@ -3107,13 +3107,13 @@
       <c r="G8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="37" t="s">
         <v>72</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="37" t="s">
         <v>137</v>
       </c>
       <c r="K8" s="1"/>
@@ -3147,11 +3147,11 @@
       <c r="G9" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J9" s="36"/>
+      <c r="J9" s="37"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
@@ -3183,11 +3183,11 @@
       <c r="G10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J10" s="36"/>
+      <c r="J10" s="37"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
@@ -3219,11 +3219,11 @@
       <c r="G11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="36"/>
+      <c r="J11" s="37"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
@@ -3255,11 +3255,11 @@
       <c r="G12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J12" s="36"/>
+      <c r="J12" s="37"/>
       <c r="K12" s="1"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
@@ -3291,11 +3291,11 @@
       <c r="G13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J13" s="36"/>
+      <c r="J13" s="37"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
@@ -3327,11 +3327,11 @@
       <c r="G14" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J14" s="36"/>
+      <c r="J14" s="37"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
         <v>62</v>
@@ -3695,13 +3695,13 @@
       <c r="G8" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="38" t="s">
         <v>72</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="38" t="s">
         <v>169</v>
       </c>
       <c r="K8" s="1"/>
@@ -3735,11 +3735,11 @@
       <c r="G9" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="37"/>
+      <c r="H9" s="38"/>
       <c r="I9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J9" s="37"/>
+      <c r="J9" s="38"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
         <v>62</v>
@@ -3771,11 +3771,11 @@
       <c r="G10" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H10" s="37"/>
+      <c r="H10" s="38"/>
       <c r="I10" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="37"/>
+      <c r="J10" s="38"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
         <v>62</v>
@@ -3807,11 +3807,11 @@
       <c r="G11" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H11" s="37"/>
+      <c r="H11" s="38"/>
       <c r="I11" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J11" s="37"/>
+      <c r="J11" s="38"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
         <v>62</v>
@@ -3843,11 +3843,11 @@
       <c r="G12" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H12" s="37"/>
+      <c r="H12" s="38"/>
       <c r="I12" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J12" s="37"/>
+      <c r="J12" s="38"/>
       <c r="K12" s="1"/>
       <c r="L12" s="15" t="s">
         <v>62</v>
@@ -3879,11 +3879,11 @@
       <c r="G13" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="38"/>
       <c r="I13" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J13" s="37"/>
+      <c r="J13" s="38"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
         <v>62</v>
@@ -3915,11 +3915,11 @@
       <c r="G14" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H14" s="37"/>
+      <c r="H14" s="38"/>
       <c r="I14" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="J14" s="37"/>
+      <c r="J14" s="38"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
         <v>62</v>
@@ -3951,11 +3951,11 @@
       <c r="G15" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="37"/>
+      <c r="H15" s="38"/>
       <c r="I15" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J15" s="37"/>
+      <c r="J15" s="38"/>
       <c r="K15" s="1"/>
       <c r="L15" s="15" t="s">
         <v>62</v>
@@ -5323,7 +5323,7 @@
         <v>290</v>
       </c>
       <c r="M42" s="33"/>
-      <c r="N42" s="38" t="s">
+      <c r="N42" s="36" t="s">
         <v>394</v>
       </c>
     </row>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FDA83B-ED6D-4EB4-9E1F-AB624EB97E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C8FF38-E5CA-4C88-AE4E-FC5DBAF62F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="751" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="VLAN 20 - Servers" sheetId="3" r:id="rId3"/>
     <sheet name="VLAN 30 - Security" sheetId="4" r:id="rId4"/>
     <sheet name="VLAN 99 - Management" sheetId="5" r:id="rId5"/>
-    <sheet name="VLAN 100 - FW-NAT" sheetId="6" r:id="rId6"/>
+    <sheet name=" FW-NAT" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VLAN 10 - End Devices'!$A$5:$A$20</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="415">
   <si>
     <t>Network Addressing Plan - VLAN Summary</t>
   </si>
@@ -1106,12 +1106,6 @@
   </si>
   <si>
     <t>sw10@2026!</t>
-  </si>
-  <si>
-    <t>VLAN 100 - Firewall / NAT</t>
-  </si>
-  <si>
-    <t>VLAN 100 - FW-NAT - fill in the yellow cells (IP, mask, gateway) manually.</t>
   </si>
   <si>
     <t>Firewall Virtual IP (gateway)</t>
@@ -1243,6 +1237,72 @@
       </rPr>
       <t>CoreEnable@2026!</t>
     </r>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>10.255.100.2</t>
+  </si>
+  <si>
+    <t>255.255.255.252</t>
+  </si>
+  <si>
+    <t>10.255.100.2/30</t>
+  </si>
+  <si>
+    <t>203.0.113.1</t>
+  </si>
+  <si>
+    <t>0001.96E1.1B01</t>
+  </si>
+  <si>
+    <t>10.255.100.6</t>
+  </si>
+  <si>
+    <t>10.255.100.6/30</t>
+  </si>
+  <si>
+    <t>0001.96E1.1B03</t>
+  </si>
+  <si>
+    <t>10.255.100.1</t>
+  </si>
+  <si>
+    <t>10.255.100.1/30</t>
+  </si>
+  <si>
+    <t>0060.2F52.A41A</t>
+  </si>
+  <si>
+    <t>10.255.100.5</t>
+  </si>
+  <si>
+    <t>10.255.100.5/30</t>
+  </si>
+  <si>
+    <t>0007.EC78.5119</t>
+  </si>
+  <si>
+    <t>192.168.10.0/24</t>
+  </si>
+  <si>
+    <t>203.0.113.2</t>
+  </si>
+  <si>
+    <t>192.168.20.0/24</t>
+  </si>
+  <si>
+    <t>192.168.99.0/24</t>
+  </si>
+  <si>
+    <t>192.168.30.0/24</t>
+  </si>
+  <si>
+    <t>192.168.20.10/32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIREWALL &amp; NAT </t>
   </si>
 </sst>
 </file>
@@ -2043,7 +2103,7 @@
       <c r="O9" s="9"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="6">
-        <f>COUNTA('VLAN 100 - FW-NAT'!B5:B80)</f>
+        <f>COUNTA(' FW-NAT'!B5:B80)</f>
         <v>11</v>
       </c>
       <c r="R9" s="7" t="s">
@@ -5128,10 +5188,10 @@
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="15"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="15"/>
@@ -5144,10 +5204,10 @@
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="15"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="15"/>
@@ -5160,10 +5220,10 @@
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="15"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
       <c r="M32" s="15"/>
@@ -5176,10 +5236,10 @@
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
       <c r="F33" s="15"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
       <c r="M33" s="15"/>
@@ -5192,10 +5252,10 @@
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
       <c r="F34" s="15"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
       <c r="M34" s="15"/>
@@ -5208,10 +5268,10 @@
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
       <c r="M35" s="15"/>
@@ -5224,10 +5284,10 @@
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="15"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
       <c r="M36" s="15"/>
@@ -5305,7 +5365,7 @@
         <v>286</v>
       </c>
       <c r="G42" s="35" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H42" s="34" t="s">
         <v>269</v>
@@ -5324,7 +5384,7 @@
       </c>
       <c r="M42" s="33"/>
       <c r="N42" s="36" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6201,13 +6261,11 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>354</v>
-      </c>
+      <c r="A2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -6263,31 +6321,43 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>356</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>358</v>
       </c>
       <c r="F5" s="12">
         <v>100</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="L5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="12"/>
+      <c r="M5" s="12" t="s">
+        <v>393</v>
+      </c>
       <c r="N5" s="14" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6295,31 +6365,43 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>212</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F6" s="12">
         <v>100</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="L6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="12"/>
+      <c r="M6" s="12" t="s">
+        <v>398</v>
+      </c>
       <c r="N6" s="14" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6327,31 +6409,43 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>217</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F7" s="12">
         <v>100</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="L7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M7" s="12"/>
+      <c r="M7" s="12" t="s">
+        <v>401</v>
+      </c>
       <c r="N7" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6359,7 +6453,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>60</v>
@@ -6368,22 +6462,34 @@
         <v>212</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F8" s="15">
         <v>100</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="L8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M8" s="17"/>
+      <c r="M8" s="17" t="s">
+        <v>404</v>
+      </c>
       <c r="N8" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6391,7 +6497,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>60</v>
@@ -6400,22 +6506,34 @@
         <v>217</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F9" s="15">
         <v>100</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="L9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="17"/>
+      <c r="M9" s="17" t="s">
+        <v>407</v>
+      </c>
       <c r="N9" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6425,11 +6543,11 @@
       <c r="D10" s="16"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="7"/>
@@ -6441,11 +6559,11 @@
       <c r="D11" s="16"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="7"/>
@@ -6457,11 +6575,11 @@
       <c r="D12" s="16"/>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="7"/>
@@ -6473,18 +6591,18 @@
       <c r="D13" s="16"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6492,25 +6610,25 @@
         <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>19</v>
@@ -6521,24 +6639,28 @@
         <v>1</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>408</v>
+      </c>
       <c r="F18" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="I18" s="16" t="s">
         <v>379</v>
-      </c>
-      <c r="G18" s="17"/>
-      <c r="H18" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6546,24 +6668,28 @@
         <v>2</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="F19" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="G19" s="17"/>
+        <v>377</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>409</v>
+      </c>
       <c r="H19" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6571,24 +6697,28 @@
         <v>3</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="F20" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="G20" s="17"/>
+        <v>377</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>409</v>
+      </c>
       <c r="H20" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6596,24 +6726,28 @@
         <v>4</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="F21" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="G21" s="17"/>
+        <v>377</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>409</v>
+      </c>
       <c r="H21" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6621,29 +6755,33 @@
         <v>5</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>413</v>
+      </c>
       <c r="F22" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="G22" s="17"/>
+        <v>377</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>409</v>
+      </c>
       <c r="H22" s="16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C8FF38-E5CA-4C88-AE4E-FC5DBAF62F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983BB1A6-A448-4783-887E-DB009D510EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="751" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="416">
   <si>
     <t>Network Addressing Plan - VLAN Summary</t>
   </si>
@@ -1303,6 +1303,9 @@
   </si>
   <si>
     <t xml:space="preserve">FIREWALL &amp; NAT </t>
+  </si>
+  <si>
+    <t>enable pwd: fw@2026!</t>
   </si>
 </sst>
 </file>
@@ -1924,11 +1927,15 @@
       <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>11</v>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>CORE-1 SVI IP</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>CORE-2 SVI IP</t>
+        </is>
       </c>
       <c r="K4" s="4" t="s">
         <v>12</v>
@@ -1965,19 +1972,67 @@
       <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="8"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.0</t>
+        </is>
+      </c>
+      <c r="E5" s="8">
+        <v>24</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>255.255.255.0</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>0.0.0.255</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.1</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.2 (CORE-1)</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.3 (CORE-2)</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.1</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.254</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>192.168.10.255</t>
+        </is>
+      </c>
+      <c r="N5" s="8">
+        <v>254</v>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>Static (no DHCP)</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="Q5" s="6">
         <f>COUNTA('VLAN 10 - End Devices'!B5:B71)</f>
         <v>16</v>
@@ -1996,19 +2051,67 @@
       <c r="C6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="8"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.0</t>
+        </is>
+      </c>
+      <c r="E6" s="8">
+        <v>24</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>255.255.255.0</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>0.0.0.255</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.1</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.2 (CORE-1)</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.3 (CORE-2)</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.1</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.254</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.20.255</t>
+        </is>
+      </c>
+      <c r="N6" s="8">
+        <v>254</v>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>Static (no DHCP)</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="Q6" s="6">
         <f>COUNTA('VLAN 20 - Servers'!B5:B80)</f>
         <v>10</v>
@@ -2027,19 +2130,67 @@
       <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="8"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.0</t>
+        </is>
+      </c>
+      <c r="E7" s="8">
+        <v>24</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>255.255.255.0</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>0.0.0.255</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.1</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.2 (CORE-1)</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.3 (CORE-2)</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.1</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.254</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>192.168.30.255</t>
+        </is>
+      </c>
+      <c r="N7" s="8">
+        <v>254</v>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>Static (no DHCP)</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="Q7" s="6">
         <f>COUNTA('VLAN 30 - Security'!B5:B80)</f>
         <v>11</v>
@@ -2058,19 +2209,67 @@
       <c r="C8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="8"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.0</t>
+        </is>
+      </c>
+      <c r="E8" s="8">
+        <v>24</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>255.255.255.0</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>0.0.0.255</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.1</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.2 (CORE-1)</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.3 (CORE-2)</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.1</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.254</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>192.168.99.255</t>
+        </is>
+      </c>
+      <c r="N8" s="8">
+        <v>254</v>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>Static (no DHCP)</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="Q8" s="6">
         <f>COUNTA('VLAN 99 - Management'!B5:B80)</f>
         <v>48</v>
@@ -2089,25 +2288,77 @@
       <c r="C9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="8"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>10.255.100.0 / 10.255.100.4</t>
+        </is>
+      </c>
+      <c r="E9" s="8">
+        <v>30</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>255.255.255.252</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>0.0.0.3</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>10.255.100.1 (CORE-1 Gi0/2)</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>10.255.100.5 (CORE-2 Gi0/1)</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>10.255.100.1 / 10.255.100.5</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>10.255.100.2 / 10.255.100.6</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>10.255.100.3 / 10.255.100.7</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>2 (per link)</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>Static (no DHCP)</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="Q9" s="6">
         <f>COUNTA(' FW-NAT'!B5:B80)</f>
         <v>11</v>
       </c>
-      <c r="R9" s="7" t="s">
-        <v>34</v>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>Two routed /30 transit links: CORE-1 to FW (Gi1/1) and CORE-2 to FW (Gi1/3). No VLAN 100 is configured; single firewall (ASA 5506-X).</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6242,14 +6493,14 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="20.6328125" customWidth="1"/>
     <col min="7" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
@@ -6320,220 +6571,350 @@
       <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F5" s="12">
-        <v>100</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>357</v>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>FW inside (Gi1/1)</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Firewall (ASA 5506-X)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>CORE-1</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Gi1/1 (inside)</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.2</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>255.255.255.252</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.2/30</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>0001.96E1.1B01</t>
+        </is>
+      </c>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>Link to CORE-1 Gi0/2 (10.255.100.0/30)</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F6" s="12">
-        <v>100</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>360</v>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>FW core2-link (Gi1/3)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Firewall (ASA 5506-X)</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>CORE-2</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Gi1/3 (core2-link)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.6</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>255.255.255.252</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.6/30</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>0001.96E1.1B03</t>
+        </is>
+      </c>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t>Link to CORE-2 Gi0/1 (10.255.100.4/30)</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F7" s="12">
-        <v>100</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>362</v>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>FW outside (Gi1/2)</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Firewall (ASA 5506-X)</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>ISP</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Gi1/2 (outside)</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>203.0.113.2</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>255.255.255.252</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>203.0.113.2/30</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>0001.96E1.1B02</t>
+        </is>
+      </c>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t>Link to ISP Gi0/0 (203.0.113.0/30); public NAT address</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="F8" s="15">
-        <v>100</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>365</v>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>CORE-1 uplink to FW</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>L3 Switch (3560-24PS)</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>CORE-1</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gi0/2 (routed)</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.1</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>255.255.255.252</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.1/30</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.2</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>0060.2F52.A41A</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>Routed interface toward firewall</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="F9" s="15">
-        <v>100</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>365</v>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>CORE-2 uplink to FW</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>L3 Switch (3560-24PS)</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>CORE-2</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Gi0/1 (routed)</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.5</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>255.255.255.252</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.5/30</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>10.255.100.6</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>0007.EC78.5119</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>Routed interface toward firewall</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6554,7 +6935,9 @@
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
+      <c r="B11" s="16" t="s">
+        <v>415</v>
+      </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="15"/>
@@ -6638,150 +7021,180 @@
       <c r="A18" s="15">
         <v>1</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>379</v>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>INTERNAL-LANS</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>PAT (overload)</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>VLANs 10, 20, 30, 99</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>192.168.0.0/16</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>outside (Gi1/2)</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>203.0.113.2</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>Interface overload</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>Via CORE-1 path (inside, Gi1/1)</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
         <v>2</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>381</v>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>INTERNAL-LANS-CORE2</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>PAT (overload)</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>VLANs 10, 20, 30, 99</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>192.168.0.0/16</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>outside (Gi1/2)</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>203.0.113.2</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>Interface overload</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>Via CORE-2 path (core2-link, Gi1/3)</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15">
         <v>3</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>383</v>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>VLAN10-NET</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>PAT (overload)</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>VLAN 10 - End Devices</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>192.168.10.0/24</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>outside (Gi1/2)</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>203.0.113.2</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>Interface overload</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>Via CORE-1 path; also covered by INTERNAL-LANS</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15">
         <v>4</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>384</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15">
-        <v>5</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>390</v>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>SERVER-1 (Server0)</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Static NAT</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>VLAN 20 - Servers</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>192.168.20.10/32</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>outside (Gi1/2)</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>203.0.114.10</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>Published externally; ISP routes 203.0.114.0/24 to FW; HTTP (tcp/80) allowed by OUTSIDE-IN</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983BB1A6-A448-4783-887E-DB009D510EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284EF510-81D6-4080-8DB3-DD21012D98EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="751" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN Summary" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="VLAN 30 - Security" sheetId="4" r:id="rId4"/>
     <sheet name="VLAN 99 - Management" sheetId="5" r:id="rId5"/>
     <sheet name=" FW-NAT" sheetId="6" r:id="rId6"/>
+    <sheet name="ISP &amp; Server6" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VLAN 10 - End Devices'!$A$5:$A$20</definedName>
@@ -39,15 +40,261 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="482">
+  <si>
+    <t xml:space="preserve">FIREWALL &amp; NAT </t>
+  </si>
+  <si>
+    <t>Enable pwd: fw@2026!</t>
+  </si>
+  <si>
+    <t>Shaded rows = gateway / infrastructure addresses. Blue = typed IPs, green = linked from VLAN Summary, yellow = fill in.</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Device Type</t>
+  </si>
+  <si>
+    <t>Connected To (Switch)</t>
+  </si>
+  <si>
+    <t>Switch Port</t>
+  </si>
+  <si>
+    <t>VLAN ID</t>
+  </si>
+  <si>
+    <t>IP Address</t>
+  </si>
+  <si>
+    <t>Subnet Mask</t>
+  </si>
+  <si>
+    <t>IP / Prefix</t>
+  </si>
+  <si>
+    <t>Default Gateway</t>
+  </si>
+  <si>
+    <t>DNS Server</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>MAC Address</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>FW inside (Gi1/1)</t>
+  </si>
+  <si>
+    <t>Firewall (ASA 5506-X)</t>
+  </si>
+  <si>
+    <t>CORE-1</t>
+  </si>
+  <si>
+    <t>Gi1/1 (inside)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>10.255.100.2</t>
+  </si>
+  <si>
+    <t>255.255.255.252</t>
+  </si>
+  <si>
+    <t>10.255.100.2/30</t>
+  </si>
+  <si>
+    <t>203.0.113.1</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>0001.96E1.1B01</t>
+  </si>
+  <si>
+    <t>Link to CORE-1 Gi0/2 (10.255.100.0/30)</t>
+  </si>
+  <si>
+    <t>FW core2-link (Gi1/3)</t>
+  </si>
+  <si>
+    <t>CORE-2</t>
+  </si>
+  <si>
+    <t>Gi1/3 (core2-link)</t>
+  </si>
+  <si>
+    <t>10.255.100.6</t>
+  </si>
+  <si>
+    <t>10.255.100.6/30</t>
+  </si>
+  <si>
+    <t>0001.96E1.1B03</t>
+  </si>
+  <si>
+    <t>Link to CORE-2 Gi0/1 (10.255.100.4/30)</t>
+  </si>
+  <si>
+    <t>FW outside (Gi1/2)</t>
+  </si>
+  <si>
+    <t>ISP</t>
+  </si>
+  <si>
+    <t>Gi1/2 (outside)</t>
+  </si>
+  <si>
+    <t>203.0.113.2</t>
+  </si>
+  <si>
+    <t>203.0.113.2/30</t>
+  </si>
+  <si>
+    <t>0001.96E1.1B02</t>
+  </si>
+  <si>
+    <t>Link to ISP Gi0/0 (203.0.113.0/30); public NAT address</t>
+  </si>
+  <si>
+    <t>CORE-1 uplink to FW</t>
+  </si>
+  <si>
+    <t>L3 Switch (3560-24PS)</t>
+  </si>
+  <si>
+    <t>Gi0/2 (routed)</t>
+  </si>
+  <si>
+    <t>10.255.100.1</t>
+  </si>
+  <si>
+    <t>10.255.100.1/30</t>
+  </si>
+  <si>
+    <t>0060.2F52.A41A</t>
+  </si>
+  <si>
+    <t>Routed interface toward firewall</t>
+  </si>
+  <si>
+    <t>CORE-2 uplink to FW</t>
+  </si>
+  <si>
+    <t>Gi0/1 (routed)</t>
+  </si>
+  <si>
+    <t>10.255.100.5</t>
+  </si>
+  <si>
+    <t>10.255.100.5/30</t>
+  </si>
+  <si>
+    <t>0007.EC78.5119</t>
+  </si>
+  <si>
+    <t>NAT Plan</t>
+  </si>
+  <si>
+    <t>Rule Name</t>
+  </si>
+  <si>
+    <t>NAT Type</t>
+  </si>
+  <si>
+    <t>Inside Network (VLAN)</t>
+  </si>
+  <si>
+    <t>Inside Local Subnet</t>
+  </si>
+  <si>
+    <t>Outside Interface</t>
+  </si>
+  <si>
+    <t>Inside Global (Public) IP</t>
+  </si>
+  <si>
+    <t>Translated Port / Pool</t>
+  </si>
+  <si>
+    <t>INTERNAL-LANS</t>
+  </si>
+  <si>
+    <t>PAT (overload)</t>
+  </si>
+  <si>
+    <t>VLANs 10, 20, 30, 99</t>
+  </si>
+  <si>
+    <t>192.168.0.0/16</t>
+  </si>
+  <si>
+    <t>outside (Gi1/2)</t>
+  </si>
+  <si>
+    <t>Interface overload</t>
+  </si>
+  <si>
+    <t>Via CORE-1 path (inside, Gi1/1)</t>
+  </si>
+  <si>
+    <t>INTERNAL-LANS-CORE2</t>
+  </si>
+  <si>
+    <t>Via CORE-2 path (core2-link, Gi1/3)</t>
+  </si>
+  <si>
+    <t>VLAN10-NET</t>
+  </si>
+  <si>
+    <t>VLAN 10 - End Devices</t>
+  </si>
+  <si>
+    <t>192.168.10.0/24</t>
+  </si>
+  <si>
+    <t>Via CORE-1 path; also covered by INTERNAL-LANS</t>
+  </si>
+  <si>
+    <t>SERVER-1 (Server0)</t>
+  </si>
+  <si>
+    <t>Static NAT</t>
+  </si>
+  <si>
+    <t>VLAN 20 - Servers</t>
+  </si>
+  <si>
+    <t>192.168.20.10/32</t>
+  </si>
+  <si>
+    <t>203.0.114.10</t>
+  </si>
+  <si>
+    <t>1:1</t>
+  </si>
+  <si>
+    <t>Published externally; ISP routes 203.0.114.0/24 to FW; HTTP (tcp/80) allowed by OUTSIDE-IN</t>
+  </si>
   <si>
     <t>Network Addressing Plan - VLAN Summary</t>
   </si>
@@ -55,9 +302,6 @@
     <t>Yellow = fill in manually. Every addressing cell is empty on purpose.</t>
   </si>
   <si>
-    <t>VLAN ID</t>
-  </si>
-  <si>
     <t>VLAN Name</t>
   </si>
   <si>
@@ -70,19 +314,16 @@
     <t>Prefix (/n)</t>
   </si>
   <si>
-    <t>Subnet Mask</t>
-  </si>
-  <si>
     <t>Wildcard Mask</t>
   </si>
   <si>
     <t>Default Gateway (HSRP VIP)</t>
   </si>
   <si>
-    <t>DIST-01 SVI IP</t>
-  </si>
-  <si>
-    <t>DIST-02 SVI IP</t>
+    <t>CORE-1 SVI IP</t>
+  </si>
+  <si>
+    <t>CORE-2 SVI IP</t>
   </si>
   <si>
     <t>First Usable</t>
@@ -100,21 +341,42 @@
     <t>DHCP Range / Assignment</t>
   </si>
   <si>
-    <t>DNS Server</t>
-  </si>
-  <si>
     <t>Entries Listed on VLAN Tab</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>End Devices</t>
   </si>
   <si>
     <t>PCs, laptops, printers, AP, phones, tablets</t>
   </si>
   <si>
+    <t>192.168.10.0</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>0.0.0.255</t>
+  </si>
+  <si>
+    <t>192.168.10.1</t>
+  </si>
+  <si>
+    <t>192.168.10.2 (CORE-1)</t>
+  </si>
+  <si>
+    <t>192.168.10.3 (CORE-2)</t>
+  </si>
+  <si>
+    <t>192.168.10.254</t>
+  </si>
+  <si>
+    <t>192.168.10.255</t>
+  </si>
+  <si>
+    <t>Static (no DHCP)</t>
+  </si>
+  <si>
     <t>Gateway on DIST-01/02 via HSRP (suggested: DIST-01 priority 110 active, DIST-02 100 standby).</t>
   </si>
   <si>
@@ -124,6 +386,24 @@
     <t>Server0 - Server5</t>
   </si>
   <si>
+    <t>192.168.20.0</t>
+  </si>
+  <si>
+    <t>192.168.20.1</t>
+  </si>
+  <si>
+    <t>192.168.20.2 (CORE-1)</t>
+  </si>
+  <si>
+    <t>192.168.20.3 (CORE-2)</t>
+  </si>
+  <si>
+    <t>192.168.20.254</t>
+  </si>
+  <si>
+    <t>192.168.20.255</t>
+  </si>
+  <si>
     <t>Same HSRP pair.</t>
   </si>
   <si>
@@ -133,6 +413,24 @@
     <t>IDS/IPS, SIEM, cameras, access control</t>
   </si>
   <si>
+    <t>192.168.30.0</t>
+  </si>
+  <si>
+    <t>192.168.30.1</t>
+  </si>
+  <si>
+    <t>192.168.30.2 (CORE-1)</t>
+  </si>
+  <si>
+    <t>192.168.30.3 (CORE-2)</t>
+  </si>
+  <si>
+    <t>192.168.30.254</t>
+  </si>
+  <si>
+    <t>192.168.30.255</t>
+  </si>
+  <si>
     <t>No security devices are drawn in the diagram - add them as needed.</t>
   </si>
   <si>
@@ -142,6 +440,24 @@
     <t>Switch / AP management (SSH, SNMP, syslog)</t>
   </si>
   <si>
+    <t>192.168.99.0</t>
+  </si>
+  <si>
+    <t>192.168.99.1</t>
+  </si>
+  <si>
+    <t>192.168.99.2 (CORE-1)</t>
+  </si>
+  <si>
+    <t>192.168.99.3 (CORE-2)</t>
+  </si>
+  <si>
+    <t>192.168.99.254</t>
+  </si>
+  <si>
+    <t>192.168.99.255</t>
+  </si>
+  <si>
     <t>Switch management SVIs. Restrict access with ACL / SSH only.</t>
   </si>
   <si>
@@ -151,63 +467,36 @@
     <t>Core &lt;-&gt; Firewall transit, NAT edge</t>
   </si>
   <si>
-    <t>Transit VLAN to firewall pair (not drawn in diagram).</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>1. All IP, mask, gateway, DHCP and DNS cells are blank for you to fill in.</t>
-  </si>
-  <si>
-    <t>2. DIST-01 / DIST-02 are assumed to be the L3 gateways (HSRP); SSW and Switch6-15 are treated as L2 with a VLAN 99 management IP only.</t>
-  </si>
-  <si>
-    <t>3. Device-to-switch attachments are read from the diagram and ports (Fa0/x) are proposed - verify them.</t>
-  </si>
-  <si>
-    <t>4. The firewall pair and VLAN 30 devices are not in the diagram.</t>
-  </si>
-  <si>
-    <t>VLAN 10 - End Devices</t>
+    <t>10.255.100.0 / 10.255.100.4</t>
+  </si>
+  <si>
+    <t>0.0.0.3</t>
+  </si>
+  <si>
+    <t>10.255.100.1 (CORE-1 Gi0/2)</t>
+  </si>
+  <si>
+    <t>10.255.100.5 (CORE-2 Gi0/1)</t>
+  </si>
+  <si>
+    <t>10.255.100.1 / 10.255.100.5</t>
+  </si>
+  <si>
+    <t>10.255.100.2 / 10.255.100.6</t>
+  </si>
+  <si>
+    <t>10.255.100.3 / 10.255.100.7</t>
+  </si>
+  <si>
+    <t>2 (per link)</t>
+  </si>
+  <si>
+    <t>Two routed /30 transit links: CORE-1 to FW (Gi1/1) and CORE-2 to FW (Gi1/3). No VLAN 100 is configured; single firewall (ASA 5506-X).</t>
   </si>
   <si>
     <t>VLAN 10 - End Devices - fill in the yellow cells (IP, mask, gateway) manually.</t>
   </si>
   <si>
-    <t>Shaded rows = gateway / infrastructure addresses. Blue = typed IPs, green = linked from VLAN Summary, yellow = fill in.</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Device Name</t>
-  </si>
-  <si>
-    <t>Device Type</t>
-  </si>
-  <si>
-    <t>Connected To (Switch)</t>
-  </si>
-  <si>
-    <t>Switch Port</t>
-  </si>
-  <si>
-    <t>IP Address</t>
-  </si>
-  <si>
-    <t>IP / Prefix</t>
-  </si>
-  <si>
-    <t>Default Gateway</t>
-  </si>
-  <si>
-    <t>Assignment</t>
-  </si>
-  <si>
-    <t>MAC Address</t>
-  </si>
-  <si>
     <t>HSRP Virtual Gateway</t>
   </si>
   <si>
@@ -229,15 +518,9 @@
     <t>DIST-01 SVI</t>
   </si>
   <si>
-    <t>L3 Switch (3560-24PS)</t>
-  </si>
-  <si>
     <t>DIST-01</t>
   </si>
   <si>
-    <t>Static</t>
-  </si>
-  <si>
     <t>HSRP Active, priority 110</t>
   </si>
   <si>
@@ -265,15 +548,9 @@
     <t>192.168.10.10</t>
   </si>
   <si>
-    <t>255.255.255.0</t>
-  </si>
-  <si>
     <t>192.168.10.10/24</t>
   </si>
   <si>
-    <t>192.168.10.1</t>
-  </si>
-  <si>
     <t>0050.0F06.73CD</t>
   </si>
   <si>
@@ -436,9 +713,6 @@
     <t>0060.4798.3C86</t>
   </si>
   <si>
-    <t>VLAN 20 - Servers</t>
-  </si>
-  <si>
     <t>VLAN 20 - Servers - fill in the yellow cells (IP, mask, gateway) manually.</t>
   </si>
   <si>
@@ -460,9 +734,6 @@
     <t>192.168.20.10/24</t>
   </si>
   <si>
-    <t>192.168.20.1</t>
-  </si>
-  <si>
     <t>0002.160E.B466</t>
   </si>
   <si>
@@ -550,24 +821,15 @@
     <t>fa0/5</t>
   </si>
   <si>
-    <t>192.169.30.10</t>
-  </si>
-  <si>
     <t>192.168.30.10/24</t>
   </si>
   <si>
-    <t>192.168.30.1</t>
-  </si>
-  <si>
     <t>0009.7C92.25B4</t>
   </si>
   <si>
     <t>Laptop1</t>
   </si>
   <si>
-    <t>192.169.30.11</t>
-  </si>
-  <si>
     <t>192.168.30.11/24</t>
   </si>
   <si>
@@ -577,9 +839,6 @@
     <t>PC1</t>
   </si>
   <si>
-    <t>192.169.30.12</t>
-  </si>
-  <si>
     <t>192.168.30.12/24</t>
   </si>
   <si>
@@ -589,9 +848,6 @@
     <t>Laptop3</t>
   </si>
   <si>
-    <t>192.169.30.13</t>
-  </si>
-  <si>
     <t>192.168.30.13/24</t>
   </si>
   <si>
@@ -601,9 +857,6 @@
     <t>Laptop4</t>
   </si>
   <si>
-    <t>192.169.30.14</t>
-  </si>
-  <si>
     <t>192.168.30.14/24</t>
   </si>
   <si>
@@ -613,9 +866,6 @@
     <t>PC3</t>
   </si>
   <si>
-    <t>192.169.30.15</t>
-  </si>
-  <si>
     <t>192.168.30.15/25</t>
   </si>
   <si>
@@ -625,9 +875,6 @@
     <t>Printer1</t>
   </si>
   <si>
-    <t>192.169.30.16</t>
-  </si>
-  <si>
     <t>192.168.30.16/26</t>
   </si>
   <si>
@@ -637,9 +884,6 @@
     <t>Printer3</t>
   </si>
   <si>
-    <t>192.169.30.17</t>
-  </si>
-  <si>
     <t>192.168.30.17/27</t>
   </si>
   <si>
@@ -685,9 +929,6 @@
     <t>Default gateway for VLAN 99</t>
   </si>
   <si>
-    <t>CORE-1</t>
-  </si>
-  <si>
     <t>L3 Switch</t>
   </si>
   <si>
@@ -697,12 +938,6 @@
     <t>Core</t>
   </si>
   <si>
-    <t>192.168.99.1</t>
-  </si>
-  <si>
-    <t>CORE-2</t>
-  </si>
-  <si>
     <t>SSH v2</t>
   </si>
   <si>
@@ -910,6 +1145,9 @@
     <t>2</t>
   </si>
   <si>
+    <t>NetAdmin@2026!</t>
+  </si>
+  <si>
     <t>0 4</t>
   </si>
   <si>
@@ -922,6 +1160,9 @@
     <t>Permit host 192.168.99.50 only</t>
   </si>
   <si>
+    <t>Enable Password is : CoreEnable@2026!</t>
+  </si>
+  <si>
     <t>labadmin</t>
   </si>
   <si>
@@ -1108,211 +1349,155 @@
     <t>sw10@2026!</t>
   </si>
   <si>
-    <t>Firewall Virtual IP (gateway)</t>
-  </si>
-  <si>
-    <t>Gateway (Firewall VIP)</t>
-  </si>
-  <si>
-    <t>FW-01 / FW-02</t>
-  </si>
-  <si>
-    <t>Inside interface</t>
-  </si>
-  <si>
-    <t>Default route target for CORE-1/2. Firewall not drawn in diagram.</t>
-  </si>
-  <si>
-    <t>FW-01 inside</t>
-  </si>
-  <si>
-    <t>Firewall</t>
-  </si>
-  <si>
-    <t>Primary firewall (active)</t>
-  </si>
-  <si>
-    <t>FW-02 inside</t>
-  </si>
-  <si>
-    <t>Secondary firewall (standby)</t>
-  </si>
-  <si>
-    <t>CORE-1 uplink to FW</t>
-  </si>
-  <si>
-    <t>SVI Vlan100</t>
-  </si>
-  <si>
-    <t>Routed interface toward firewall</t>
-  </si>
-  <si>
-    <t>CORE-2 uplink to FW</t>
-  </si>
-  <si>
-    <t>NAT Plan</t>
-  </si>
-  <si>
-    <t>Rule Name</t>
-  </si>
-  <si>
-    <t>NAT Type</t>
-  </si>
-  <si>
-    <t>Inside Network (VLAN)</t>
-  </si>
-  <si>
-    <t>Inside Local Subnet</t>
-  </si>
-  <si>
-    <t>Outside Interface</t>
-  </si>
-  <si>
-    <t>Inside Global (Public) IP</t>
-  </si>
-  <si>
-    <t>Translated Port / Pool</t>
-  </si>
-  <si>
-    <t>PAT-VLAN10</t>
-  </si>
-  <si>
-    <t>PAT (overload)</t>
-  </si>
-  <si>
-    <t>FW outside (to ISP)</t>
-  </si>
-  <si>
-    <t>Interface overload</t>
-  </si>
-  <si>
-    <t>Internet access for users</t>
-  </si>
-  <si>
-    <t>PAT-VLAN20</t>
-  </si>
-  <si>
-    <t>Outbound updates only</t>
-  </si>
-  <si>
-    <t>PAT-VLAN99</t>
-  </si>
-  <si>
-    <t>Optional - for NTP / updates</t>
-  </si>
-  <si>
-    <t>PAT-VLAN30</t>
-  </si>
-  <si>
-    <t>Optional - for threat feeds</t>
-  </si>
-  <si>
-    <t>STATIC-Server0</t>
-  </si>
-  <si>
-    <t>Static NAT</t>
-  </si>
-  <si>
-    <t>1:1</t>
-  </si>
-  <si>
-    <t>Only if Server0 is published externally</t>
-  </si>
-  <si>
-    <t>Fill the yellow cells with the public IP(s) from your ISP. Firewall interface names/IPs are assumptions - the firewall is not in the diagram.</t>
-  </si>
-  <si>
-    <t>NetAdmin@2026!</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Enable Password is : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CoreEnable@2026!</t>
-    </r>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>10.255.100.2</t>
-  </si>
-  <si>
-    <t>255.255.255.252</t>
-  </si>
-  <si>
-    <t>10.255.100.2/30</t>
-  </si>
-  <si>
-    <t>203.0.113.1</t>
-  </si>
-  <si>
-    <t>0001.96E1.1B01</t>
-  </si>
-  <si>
-    <t>10.255.100.6</t>
-  </si>
-  <si>
-    <t>10.255.100.6/30</t>
-  </si>
-  <si>
-    <t>0001.96E1.1B03</t>
-  </si>
-  <si>
-    <t>10.255.100.1</t>
-  </si>
-  <si>
-    <t>10.255.100.1/30</t>
-  </si>
-  <si>
-    <t>0060.2F52.A41A</t>
-  </si>
-  <si>
-    <t>10.255.100.5</t>
-  </si>
-  <si>
-    <t>10.255.100.5/30</t>
-  </si>
-  <si>
-    <t>0007.EC78.5119</t>
-  </si>
-  <si>
-    <t>192.168.10.0/24</t>
-  </si>
-  <si>
-    <t>203.0.113.2</t>
-  </si>
-  <si>
-    <t>192.168.20.0/24</t>
-  </si>
-  <si>
-    <t>192.168.99.0/24</t>
-  </si>
-  <si>
-    <t>192.168.30.0/24</t>
-  </si>
-  <si>
-    <t>192.168.20.10/32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIREWALL &amp; NAT </t>
-  </si>
-  <si>
-    <t>enable pwd: fw@2026!</t>
+    <t>ISP &amp; SERVER6 (External / Internet Side)</t>
+  </si>
+  <si>
+    <t>Values read from the Packet Tracer file (Redundancy_ARCH.pkt). Outside the internal 192.168.0.0/16 addressing plan; not part of any VLAN.</t>
+  </si>
+  <si>
+    <t>Connected To</t>
+  </si>
+  <si>
+    <t>Interface / Port</t>
+  </si>
+  <si>
+    <t>ISP Gi0/0 (to FW)</t>
+  </si>
+  <si>
+    <t>Router (2911)</t>
+  </si>
+  <si>
+    <t>FW (ASA 5506-X) Gi1/2 outside</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0</t>
+  </si>
+  <si>
+    <t>203.0.113.1/30</t>
+  </si>
+  <si>
+    <t>0030.A33E.BE01</t>
+  </si>
+  <si>
+    <t>Point-to-point link to firewall outside interface (203.0.113.0/30)</t>
+  </si>
+  <si>
+    <t>ISP Gi0/1 (to Server6)</t>
+  </si>
+  <si>
+    <t>Server6</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/1</t>
+  </si>
+  <si>
+    <t>198.51.100.1</t>
+  </si>
+  <si>
+    <t>198.51.100.1/24</t>
+  </si>
+  <si>
+    <t>0030.A33E.BE02</t>
+  </si>
+  <si>
+    <t>Gateway for the internet-side server network (198.51.100.0/24)</t>
+  </si>
+  <si>
+    <t>ISP Gi0/2 (unused)</t>
+  </si>
+  <si>
+    <t>Not connected</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/2</t>
+  </si>
+  <si>
+    <t>No IP</t>
+  </si>
+  <si>
+    <t>0030.A33E.BE03</t>
+  </si>
+  <si>
+    <t>Administratively shut down, no IP address</t>
+  </si>
+  <si>
+    <t>FastEthernet0 -&gt; ISP Gi0/1</t>
+  </si>
+  <si>
+    <t>198.51.100.10</t>
+  </si>
+  <si>
+    <t>198.51.100.10/24</t>
+  </si>
+  <si>
+    <t>0.0.0.0 (none set)</t>
+  </si>
+  <si>
+    <t>00E0.A360.E60C</t>
+  </si>
+  <si>
+    <t>Internet-side server. Services enabled: HTTP, FTP, NTP, Syslog. Straight-through cable to ISP Gi0/1</t>
+  </si>
+  <si>
+    <t>ISP Static Routes</t>
+  </si>
+  <si>
+    <t>Destination Network</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>Next Hop</t>
+  </si>
+  <si>
+    <t>192.168.0.0</t>
+  </si>
+  <si>
+    <t>255.255.0.0</t>
+  </si>
+  <si>
+    <t>Return route to all internal VLANs via FW outside</t>
+  </si>
+  <si>
+    <t>203.0.114.0</t>
+  </si>
+  <si>
+    <t>Public static-NAT range (Server0 = 203.0.114.10) routed to FW</t>
+  </si>
+  <si>
+    <t>Note: ISP-side default route / NAT is not configured on the ISP router; it only holds the two static routes above.</t>
+  </si>
+  <si>
+    <t>192.168.30.10</t>
+  </si>
+  <si>
+    <t>192.168.30.11</t>
+  </si>
+  <si>
+    <t>192.168.30.12</t>
+  </si>
+  <si>
+    <t>192.168.30.13</t>
+  </si>
+  <si>
+    <t>192.168.30.14</t>
+  </si>
+  <si>
+    <t>192.168.30.15</t>
+  </si>
+  <si>
+    <t>192.168.30.16</t>
+  </si>
+  <si>
+    <t>192.168.30.17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1385,13 +1570,34 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1440,8 +1646,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7EEF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1497,12 +1713,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1600,9 +1844,20 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1894,72 +2149,68 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>CORE-1 SVI IP</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>CORE-2 SVI IP</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="L4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -1967,78 +2218,56 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.0</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="E5" s="8">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>255.255.255.0</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>0.0.0.255</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.1</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.2 (CORE-1)</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.3 (CORE-2)</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.1</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.254</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>192.168.10.255</t>
-        </is>
+      <c r="F5" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="N5" s="8">
         <v>254</v>
       </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>Static (no DHCP)</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="O5" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="Q5" s="6">
         <f>COUNTA('VLAN 10 - End Devices'!B5:B71)</f>
         <v>16</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2046,78 +2275,56 @@
         <v>20</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.0</t>
-        </is>
+        <v>112</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="E6" s="8">
         <v>24</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>255.255.255.0</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>0.0.0.255</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.1</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.2 (CORE-1)</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.3 (CORE-2)</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.1</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.254</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>192.168.20.255</t>
-        </is>
+      <c r="F6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>118</v>
       </c>
       <c r="N6" s="8">
         <v>254</v>
       </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>Static (no DHCP)</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="O6" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="Q6" s="6">
         <f>COUNTA('VLAN 20 - Servers'!B5:B80)</f>
         <v>10</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2125,78 +2332,56 @@
         <v>30</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.0</t>
-        </is>
+        <v>121</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="E7" s="8">
         <v>24</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>255.255.255.0</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>0.0.0.255</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.1</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.2 (CORE-1)</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.3 (CORE-2)</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.1</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.254</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>192.168.30.255</t>
-        </is>
+      <c r="F7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="N7" s="8">
         <v>254</v>
       </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>Static (no DHCP)</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="O7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="Q7" s="6">
         <f>COUNTA('VLAN 30 - Security'!B5:B80)</f>
         <v>11</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2204,78 +2389,56 @@
         <v>99</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.0</t>
-        </is>
+        <v>130</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="E8" s="8">
         <v>24</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>255.255.255.0</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>0.0.0.255</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.1</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.2 (CORE-1)</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.3 (CORE-2)</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.1</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.254</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>192.168.99.255</t>
-        </is>
+      <c r="F8" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="N8" s="8">
         <v>254</v>
       </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
-          <t>Static (no DHCP)</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="O8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="Q8" s="6">
         <f>COUNTA('VLAN 99 - Management'!B5:B80)</f>
         <v>48</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2283,108 +2446,72 @@
         <v>100</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>10.255.100.0 / 10.255.100.4</t>
-        </is>
+        <v>139</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="E9" s="8">
         <v>30</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>255.255.255.252</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>0.0.0.3</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>10.255.100.1 (CORE-1 Gi0/2)</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>10.255.100.5 (CORE-2 Gi0/1)</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>10.255.100.1 / 10.255.100.5</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>10.255.100.2 / 10.255.100.6</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>10.255.100.3 / 10.255.100.7</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>2 (per link)</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>Static (no DHCP)</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="Q9" s="6">
         <f>COUNTA(' FW-NAT'!B5:B80)</f>
-        <v>11</v>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>Two routed /30 transit links: CORE-1 to FW (Gi1/1) and CORE-2 to FW (Gi1/3). No VLAN 100 is configured; single firewall (ASA 5506-X).</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
-        <v>35</v>
-      </c>
+      <c r="A11" s="10"/>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>36</v>
-      </c>
+      <c r="A12" s="11"/>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>37</v>
-      </c>
+      <c r="A13" s="11"/>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="A14" s="11"/>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>39</v>
-      </c>
+      <c r="A15" s="11"/>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
@@ -2419,61 +2546,61 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2481,16 +2608,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F5" s="12">
         <v>10</v>
@@ -2501,11 +2628,11 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="14" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2513,16 +2640,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F6" s="12">
         <v>10</v>
@@ -2533,11 +2660,11 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="14" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2545,16 +2672,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F7" s="12">
         <v>10</v>
@@ -2565,11 +2692,11 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M7" s="12"/>
       <c r="N7" s="14" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2577,38 +2704,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F8" s="15">
         <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>72</v>
+        <v>166</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>102</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>74</v>
+        <v>167</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>104</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="N8" s="7"/>
     </row>
@@ -2617,34 +2744,34 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F9" s="15">
         <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="37"/>
+        <v>172</v>
+      </c>
+      <c r="H9" s="43"/>
       <c r="I9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="37"/>
+        <v>173</v>
+      </c>
+      <c r="J9" s="43"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="N9" s="7"/>
     </row>
@@ -2653,34 +2780,34 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F10" s="15">
         <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="37"/>
+        <v>178</v>
+      </c>
+      <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="37"/>
+        <v>179</v>
+      </c>
+      <c r="J10" s="43"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="N10" s="7"/>
     </row>
@@ -2689,34 +2816,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F11" s="15">
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="37"/>
+        <v>183</v>
+      </c>
+      <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="37"/>
+        <v>183</v>
+      </c>
+      <c r="J11" s="43"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="N11" s="7"/>
     </row>
@@ -2725,35 +2852,35 @@
         <v>13</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F12" s="19">
         <v>10</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="37"/>
+        <v>187</v>
+      </c>
+      <c r="H12" s="43"/>
       <c r="I12" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="J12" s="37"/>
+        <v>187</v>
+      </c>
+      <c r="J12" s="43"/>
       <c r="K12" s="19"/>
       <c r="L12" s="19" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M12" s="19"/>
       <c r="N12" s="21" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2761,34 +2888,34 @@
         <v>15</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F13" s="15">
         <v>10</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="37"/>
+        <v>191</v>
+      </c>
+      <c r="H13" s="43"/>
       <c r="I13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="37"/>
+        <v>191</v>
+      </c>
+      <c r="J13" s="43"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="N13" s="7"/>
     </row>
@@ -2797,34 +2924,34 @@
         <v>17</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F14" s="15">
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="37"/>
+        <v>195</v>
+      </c>
+      <c r="H14" s="43"/>
       <c r="I14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J14" s="37"/>
+        <v>195</v>
+      </c>
+      <c r="J14" s="43"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="N14" s="7"/>
     </row>
@@ -2833,34 +2960,34 @@
         <v>18</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F15" s="15">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="37"/>
+        <v>198</v>
+      </c>
+      <c r="H15" s="43"/>
       <c r="I15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J15" s="37"/>
+        <v>198</v>
+      </c>
+      <c r="J15" s="43"/>
       <c r="K15" s="1"/>
       <c r="L15" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="N15" s="7"/>
     </row>
@@ -2869,34 +2996,34 @@
         <v>19</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F16" s="15">
         <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="37"/>
+        <v>202</v>
+      </c>
+      <c r="H16" s="43"/>
       <c r="I16" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J16" s="37"/>
+        <v>202</v>
+      </c>
+      <c r="J16" s="43"/>
       <c r="K16" s="1"/>
       <c r="L16" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="N16" s="7"/>
     </row>
@@ -2905,34 +3032,34 @@
         <v>20</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F17" s="15">
         <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" s="37"/>
+        <v>205</v>
+      </c>
+      <c r="H17" s="43"/>
       <c r="I17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J17" s="37"/>
+        <v>205</v>
+      </c>
+      <c r="J17" s="43"/>
       <c r="K17" s="1"/>
       <c r="L17" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="N17" s="7"/>
     </row>
@@ -2941,34 +3068,34 @@
         <v>22</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F18" s="15">
         <v>10</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18" s="37"/>
+        <v>209</v>
+      </c>
+      <c r="H18" s="43"/>
       <c r="I18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J18" s="37"/>
+        <v>209</v>
+      </c>
+      <c r="J18" s="43"/>
       <c r="K18" s="1"/>
       <c r="L18" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>117</v>
+        <v>210</v>
       </c>
       <c r="N18" s="7"/>
     </row>
@@ -2977,37 +3104,37 @@
         <v>24</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>118</v>
+        <v>211</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>119</v>
+        <v>212</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="F19" s="15">
         <v>10</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="37"/>
+        <v>215</v>
+      </c>
+      <c r="H19" s="43"/>
       <c r="I19" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J19" s="37"/>
+        <v>215</v>
+      </c>
+      <c r="J19" s="43"/>
       <c r="K19" s="1"/>
       <c r="L19" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>123</v>
+        <v>216</v>
       </c>
       <c r="N19" s="23" t="s">
-        <v>124</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3015,37 +3142,37 @@
         <v>25</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>126</v>
+        <v>219</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="F20" s="15">
         <v>10</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H20" s="37"/>
+        <v>220</v>
+      </c>
+      <c r="H20" s="44"/>
       <c r="I20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J20" s="37"/>
+        <v>220</v>
+      </c>
+      <c r="J20" s="44"/>
       <c r="K20" s="1"/>
       <c r="L20" s="15" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="N20" s="23" t="s">
-        <v>124</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3243,61 +3370,61 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3305,16 +3432,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="F5" s="12">
         <v>20</v>
@@ -3325,11 +3452,11 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="14" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3337,16 +3464,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="F6" s="12">
         <v>20</v>
@@ -3357,11 +3484,11 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="14" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3369,16 +3496,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="F7" s="12">
         <v>20</v>
@@ -3389,11 +3516,11 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M7" s="12"/>
       <c r="N7" s="14" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3401,38 +3528,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F8" s="15">
         <v>20</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>72</v>
+        <v>227</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>102</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>137</v>
+        <v>228</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>114</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>138</v>
+        <v>229</v>
       </c>
       <c r="N8" s="7"/>
     </row>
@@ -3441,34 +3568,34 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F9" s="15">
         <v>20</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H9" s="37"/>
+        <v>232</v>
+      </c>
+      <c r="H9" s="43"/>
       <c r="I9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J9" s="37"/>
+        <v>233</v>
+      </c>
+      <c r="J9" s="43"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="N9" s="7"/>
     </row>
@@ -3477,34 +3604,34 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="F10" s="15">
         <v>20</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="37"/>
+        <v>237</v>
+      </c>
+      <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10" s="37"/>
+        <v>237</v>
+      </c>
+      <c r="J10" s="43"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="N10" s="7"/>
     </row>
@@ -3513,34 +3640,34 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F11" s="15">
         <v>20</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H11" s="37"/>
+        <v>240</v>
+      </c>
+      <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J11" s="37"/>
+        <v>240</v>
+      </c>
+      <c r="J11" s="43"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="N11" s="7"/>
     </row>
@@ -3549,34 +3676,34 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>151</v>
+        <v>242</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F12" s="15">
         <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H12" s="37"/>
+        <v>244</v>
+      </c>
+      <c r="H12" s="43"/>
       <c r="I12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J12" s="37"/>
+        <v>244</v>
+      </c>
+      <c r="J12" s="43"/>
       <c r="K12" s="1"/>
       <c r="L12" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="N12" s="7"/>
     </row>
@@ -3585,34 +3712,34 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>155</v>
+        <v>246</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="F13" s="15">
         <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H13" s="37"/>
+        <v>247</v>
+      </c>
+      <c r="H13" s="43"/>
       <c r="I13" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" s="37"/>
+        <v>247</v>
+      </c>
+      <c r="J13" s="43"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="N13" s="7"/>
     </row>
@@ -3621,34 +3748,34 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F14" s="15">
         <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H14" s="37"/>
+        <v>250</v>
+      </c>
+      <c r="H14" s="44"/>
       <c r="I14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J14" s="37"/>
+        <v>250</v>
+      </c>
+      <c r="J14" s="44"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="N14" s="7"/>
     </row>
@@ -3799,8 +3926,8 @@
   </sheetData>
   <autoFilter ref="A4:N23" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="2">
+    <mergeCell ref="J8:J14"/>
     <mergeCell ref="H8:H14"/>
-    <mergeCell ref="J8:J14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3831,61 +3958,61 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>161</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>162</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3893,16 +4020,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="F5" s="12">
         <v>30</v>
@@ -3913,11 +4040,11 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="14" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3925,16 +4052,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="F6" s="12">
         <v>30</v>
@@ -3945,11 +4072,11 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="14" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3957,16 +4084,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="F7" s="12">
         <v>30</v>
@@ -3977,11 +4104,11 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="12" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M7" s="12"/>
       <c r="N7" s="14" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3989,38 +4116,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="F8" s="15">
         <v>30</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>72</v>
+        <v>474</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>102</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>169</v>
+        <v>258</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>123</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="N8" s="7"/>
     </row>
@@ -4029,34 +4156,34 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="F9" s="15">
         <v>30</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" s="38"/>
+        <v>475</v>
+      </c>
+      <c r="H9" s="43"/>
       <c r="I9" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="38"/>
+        <v>261</v>
+      </c>
+      <c r="J9" s="43"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="N9" s="7"/>
     </row>
@@ -4065,34 +4192,34 @@
         <v>6</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F10" s="15">
         <v>30</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H10" s="38"/>
+        <v>476</v>
+      </c>
+      <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J10" s="38"/>
+        <v>264</v>
+      </c>
+      <c r="J10" s="43"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="N10" s="7"/>
     </row>
@@ -4101,34 +4228,34 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="F11" s="15">
         <v>30</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H11" s="38"/>
+        <v>477</v>
+      </c>
+      <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J11" s="38"/>
+        <v>267</v>
+      </c>
+      <c r="J11" s="43"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="N11" s="7"/>
     </row>
@@ -4137,34 +4264,34 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>183</v>
+        <v>269</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F12" s="15">
         <v>30</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H12" s="38"/>
+        <v>478</v>
+      </c>
+      <c r="H12" s="43"/>
       <c r="I12" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J12" s="38"/>
+        <v>270</v>
+      </c>
+      <c r="J12" s="43"/>
       <c r="K12" s="1"/>
       <c r="L12" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="N12" s="7"/>
     </row>
@@ -4173,34 +4300,34 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>187</v>
+        <v>272</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="F13" s="15">
         <v>30</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="38"/>
+        <v>479</v>
+      </c>
+      <c r="H13" s="43"/>
       <c r="I13" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J13" s="38"/>
+        <v>273</v>
+      </c>
+      <c r="J13" s="43"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>190</v>
+        <v>274</v>
       </c>
       <c r="N13" s="7"/>
     </row>
@@ -4209,34 +4336,34 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="F14" s="15">
         <v>30</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H14" s="38"/>
+        <v>480</v>
+      </c>
+      <c r="H14" s="43"/>
       <c r="I14" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J14" s="38"/>
+        <v>276</v>
+      </c>
+      <c r="J14" s="43"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="N14" s="7"/>
     </row>
@@ -4245,34 +4372,34 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>195</v>
+        <v>278</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="F15" s="15">
         <v>30</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H15" s="38"/>
+        <v>481</v>
+      </c>
+      <c r="H15" s="43"/>
       <c r="I15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J15" s="38"/>
+        <v>279</v>
+      </c>
+      <c r="J15" s="43"/>
       <c r="K15" s="1"/>
       <c r="L15" s="15" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>198</v>
+        <v>280</v>
       </c>
       <c r="N15" s="7"/>
     </row>
@@ -4346,6 +4473,7 @@
     <mergeCell ref="H8:H15"/>
     <mergeCell ref="J8:J15"/>
   </mergeCells>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4375,61 +4503,61 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>199</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>200</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>203</v>
+        <v>285</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>204</v>
+        <v>286</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>205</v>
+        <v>287</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>208</v>
+        <v>290</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4437,16 +4565,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="F5" s="12">
         <v>99</v>
@@ -4456,16 +4584,16 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="13" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>211</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4473,36 +4601,36 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="F6" s="15">
         <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="16" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N6" s="16"/>
     </row>
@@ -4511,38 +4639,38 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="F7" s="15">
         <v>99</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>219</v>
+        <v>298</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N7" s="16"/>
     </row>
@@ -4551,41 +4679,41 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="F8" s="15">
         <v>99</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4593,41 +4721,41 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="F9" s="15">
         <v>99</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>226</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4635,38 +4763,38 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F10" s="15">
         <v>99</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>230</v>
+        <v>309</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>231</v>
+        <v>310</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N10" s="16"/>
     </row>
@@ -4675,38 +4803,38 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F11" s="15">
         <v>99</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>233</v>
+        <v>312</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N11" s="16"/>
     </row>
@@ -4715,38 +4843,38 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F12" s="15">
         <v>99</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N12" s="16"/>
     </row>
@@ -4755,38 +4883,38 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F13" s="15">
         <v>99</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N13" s="16"/>
     </row>
@@ -4795,38 +4923,38 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F14" s="15">
         <v>99</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>240</v>
+        <v>319</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N14" s="16"/>
     </row>
@@ -4835,38 +4963,38 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F15" s="15">
         <v>99</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N15" s="16"/>
     </row>
@@ -4875,38 +5003,38 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F16" s="15">
         <v>99</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>246</v>
+        <v>325</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N16" s="16"/>
     </row>
@@ -4915,38 +5043,38 @@
         <v>13</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="F17" s="15">
         <v>99</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>248</v>
+        <v>327</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N17" s="16"/>
     </row>
@@ -4955,38 +5083,38 @@
         <v>14</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F18" s="15">
         <v>99</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N18" s="16"/>
     </row>
@@ -4995,38 +5123,38 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F19" s="15">
         <v>99</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N19" s="16"/>
     </row>
@@ -5035,38 +5163,38 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F20" s="15">
         <v>99</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N20" s="16"/>
     </row>
@@ -5075,38 +5203,38 @@
         <v>17</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F21" s="15">
         <v>99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N21" s="16"/>
     </row>
@@ -5115,38 +5243,38 @@
         <v>18</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F22" s="15">
         <v>99</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>256</v>
+        <v>335</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="M22" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N22" s="16"/>
     </row>
@@ -5155,38 +5283,38 @@
         <v>19</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F23" s="15">
         <v>99</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N23" s="16"/>
     </row>
@@ -5195,38 +5323,38 @@
         <v>20</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F24" s="15">
         <v>99</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>258</v>
+        <v>337</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N24" s="16"/>
     </row>
@@ -5235,38 +5363,38 @@
         <v>21</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F25" s="15">
         <v>99</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N25" s="16"/>
     </row>
@@ -5275,38 +5403,38 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F26" s="15">
         <v>99</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>260</v>
+        <v>339</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N26" s="16"/>
     </row>
@@ -5315,38 +5443,38 @@
         <v>23</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="F27" s="15">
         <v>99</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>261</v>
+        <v>340</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N27" s="16"/>
     </row>
@@ -5355,16 +5483,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>262</v>
+        <v>341</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>264</v>
+        <v>343</v>
       </c>
       <c r="F28" s="27">
         <v>99</v>
@@ -5374,20 +5502,20 @@
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
       <c r="K28" s="28" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="M28" s="27" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N28" s="28" t="s">
-        <v>265</v>
+        <v>344</v>
       </c>
       <c r="O28" s="22"/>
       <c r="P28" s="30" t="s">
-        <v>266</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5395,41 +5523,41 @@
         <v>25</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="F29" s="17">
         <v>99</v>
       </c>
       <c r="G29" s="32" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="32" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
       <c r="L29" s="31" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="N29" s="31" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5546,54 +5674,54 @@
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>273</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>274</v>
+        <v>353</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>278</v>
+        <v>357</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>279</v>
+        <v>358</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>281</v>
+        <v>360</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>283</v>
+        <v>362</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>284</v>
+        <v>363</v>
       </c>
       <c r="M41" s="33"/>
       <c r="N41" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5601,41 +5729,41 @@
         <v>1</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>285</v>
+        <v>364</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G42" s="35" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="H42" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M42" s="33"/>
       <c r="N42" s="36" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -5643,37 +5771,37 @@
         <v>2</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>219</v>
+        <v>298</v>
       </c>
       <c r="E43" s="34" t="s">
-        <v>291</v>
+        <v>372</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>292</v>
+        <v>373</v>
       </c>
       <c r="H43" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M43" s="33"/>
       <c r="N43" s="16"/>
@@ -5683,37 +5811,37 @@
         <v>3</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>293</v>
+        <v>374</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>294</v>
+        <v>375</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="H44" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M44" s="33"/>
       <c r="N44" s="16"/>
@@ -5723,37 +5851,37 @@
         <v>4</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>296</v>
+        <v>377</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="E45" s="34" t="s">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>298</v>
+        <v>379</v>
       </c>
       <c r="H45" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M45" s="33"/>
       <c r="N45" s="16"/>
@@ -5763,37 +5891,37 @@
         <v>5</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>299</v>
+        <v>380</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>230</v>
+        <v>309</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>300</v>
+        <v>381</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>301</v>
+        <v>382</v>
       </c>
       <c r="H46" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M46" s="33"/>
       <c r="N46" s="16"/>
@@ -5803,37 +5931,37 @@
         <v>6</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>233</v>
+        <v>312</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="H47" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M47" s="33"/>
       <c r="N47" s="16"/>
@@ -5843,37 +5971,37 @@
         <v>7</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>305</v>
+        <v>386</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="E48" s="34" t="s">
-        <v>306</v>
+        <v>387</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>307</v>
+        <v>388</v>
       </c>
       <c r="H48" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M48" s="33"/>
       <c r="N48" s="16"/>
@@ -5883,37 +6011,37 @@
         <v>8</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>308</v>
+        <v>389</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>309</v>
+        <v>390</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="H49" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M49" s="33"/>
       <c r="N49" s="16"/>
@@ -5923,37 +6051,37 @@
         <v>9</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>311</v>
+        <v>392</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>240</v>
+        <v>319</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>312</v>
+        <v>393</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="H50" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M50" s="33"/>
       <c r="N50" s="16"/>
@@ -5963,37 +6091,37 @@
         <v>10</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>314</v>
+        <v>395</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>315</v>
+        <v>396</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>316</v>
+        <v>397</v>
       </c>
       <c r="H51" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M51" s="33"/>
       <c r="N51" s="16"/>
@@ -6003,37 +6131,37 @@
         <v>11</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>317</v>
+        <v>398</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>246</v>
+        <v>325</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>318</v>
+        <v>399</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="H52" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M52" s="33"/>
       <c r="N52" s="16"/>
@@ -6043,37 +6171,37 @@
         <v>12</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>320</v>
+        <v>401</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>248</v>
+        <v>327</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>321</v>
+        <v>402</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>322</v>
+        <v>403</v>
       </c>
       <c r="H53" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M53" s="33"/>
       <c r="N53" s="16"/>
@@ -6083,37 +6211,37 @@
         <v>13</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>323</v>
+        <v>404</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>324</v>
+        <v>405</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>325</v>
+        <v>406</v>
       </c>
       <c r="H54" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M54" s="33"/>
       <c r="N54" s="16"/>
@@ -6123,37 +6251,37 @@
         <v>14</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>327</v>
+        <v>408</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>328</v>
+        <v>409</v>
       </c>
       <c r="H55" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M55" s="33"/>
       <c r="N55" s="16"/>
@@ -6163,37 +6291,37 @@
         <v>15</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="H56" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M56" s="33"/>
       <c r="N56" s="16"/>
@@ -6203,37 +6331,37 @@
         <v>16</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="E57" s="34" t="s">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>334</v>
+        <v>415</v>
       </c>
       <c r="H57" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M57" s="33"/>
       <c r="N57" s="16"/>
@@ -6243,37 +6371,37 @@
         <v>17</v>
       </c>
       <c r="B58" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58" s="34" t="s">
-        <v>256</v>
-      </c>
       <c r="E58" s="34" t="s">
-        <v>336</v>
+        <v>417</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>337</v>
+        <v>418</v>
       </c>
       <c r="H58" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M58" s="33"/>
       <c r="N58" s="16"/>
@@ -6283,37 +6411,37 @@
         <v>18</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>340</v>
+        <v>421</v>
       </c>
       <c r="H59" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M59" s="33"/>
       <c r="N59" s="16"/>
@@ -6323,37 +6451,37 @@
         <v>19</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>341</v>
+        <v>422</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>258</v>
+        <v>337</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>343</v>
+        <v>424</v>
       </c>
       <c r="H60" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I60" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M60" s="33"/>
       <c r="N60" s="16"/>
@@ -6363,37 +6491,37 @@
         <v>20</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>344</v>
+        <v>425</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>346</v>
+        <v>427</v>
       </c>
       <c r="H61" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M61" s="33"/>
       <c r="N61" s="16"/>
@@ -6403,37 +6531,37 @@
         <v>21</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>347</v>
+        <v>428</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>260</v>
+        <v>339</v>
       </c>
       <c r="E62" s="34" t="s">
+        <v>429</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H62" s="34" t="s">
         <v>348</v>
       </c>
-      <c r="F62" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H62" s="34" t="s">
-        <v>269</v>
-      </c>
       <c r="I62" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M62" s="33"/>
       <c r="N62" s="16"/>
@@ -6443,37 +6571,37 @@
         <v>22</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="D63" s="34" t="s">
-        <v>261</v>
+        <v>340</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>351</v>
+        <v>432</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>352</v>
+        <v>433</v>
       </c>
       <c r="H63" s="34" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="M63" s="33"/>
       <c r="N63" s="16"/>
@@ -6481,7 +6609,7 @@
   </sheetData>
   <autoFilter ref="A4:N36" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <hyperlinks>
-    <hyperlink ref="G42" r:id="rId1" xr:uid="{6674457B-8AF6-4F62-A8EA-B7F318167614}"/>
+    <hyperlink ref="G42" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6512,7 +6640,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>414</v>
+        <v>0</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6520,401 +6651,271 @@
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>FW inside (Gi1/1)</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Firewall (ASA 5506-X)</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>CORE-1</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Gi1/1 (inside)</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.2</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>255.255.255.252</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.2/30</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>203.0.113.1</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>0001.96E1.1B01</t>
-        </is>
-      </c>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>Link to CORE-1 Gi0/2 (10.255.100.0/30)</t>
-        </is>
+      <c r="B5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>FW core2-link (Gi1/3)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Firewall (ASA 5506-X)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>CORE-2</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Gi1/3 (core2-link)</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.6</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>255.255.255.252</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.6/30</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>203.0.113.1</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>0001.96E1.1B03</t>
-        </is>
-      </c>
-      <c r="N6" s="14" t="inlineStr">
-        <is>
-          <t>Link to CORE-2 Gi0/1 (10.255.100.4/30)</t>
-        </is>
+      <c r="B6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>FW outside (Gi1/2)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Firewall (ASA 5506-X)</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>ISP</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Gi1/2 (outside)</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>203.0.113.2</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>255.255.255.252</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>203.0.113.2/30</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>203.0.113.1</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>0001.96E1.1B02</t>
-        </is>
-      </c>
-      <c r="N7" s="14" t="inlineStr">
-        <is>
-          <t>Link to ISP Gi0/0 (203.0.113.0/30); public NAT address</t>
-        </is>
+      <c r="B7" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>CORE-1 uplink to FW</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>L3 Switch (3560-24PS)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>CORE-1</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Gi0/2 (routed)</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.1</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>255.255.255.252</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.1/30</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.2</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>0060.2F52.A41A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>Routed interface toward firewall</t>
-        </is>
+      <c r="B8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>CORE-2 uplink to FW</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>L3 Switch (3560-24PS)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>CORE-2</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Gi0/1 (routed)</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.5</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>255.255.255.252</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.5/30</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>10.255.100.6</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>0007.EC78.5119</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>Routed interface toward firewall</t>
-        </is>
+      <c r="B9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6935,9 +6936,7 @@
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15"/>
-      <c r="B11" s="16" t="s">
-        <v>415</v>
-      </c>
+      <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="15"/>
@@ -6985,220 +6984,469 @@
     </row>
     <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>367</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>369</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>370</v>
+        <v>58</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>371</v>
+        <v>59</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>372</v>
+        <v>60</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>373</v>
+        <v>61</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>374</v>
+        <v>62</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
         <v>1</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>INTERNAL-LANS</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>PAT (overload)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>VLANs 10, 20, 30, 99</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>192.168.0.0/16</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>outside (Gi1/2)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>203.0.113.2</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>Interface overload</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>Via CORE-1 path (inside, Gi1/1)</t>
-        </is>
+      <c r="B18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
         <v>2</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>INTERNAL-LANS-CORE2</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>PAT (overload)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>VLANs 10, 20, 30, 99</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>192.168.0.0/16</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>outside (Gi1/2)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>203.0.113.2</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>Interface overload</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>Via CORE-2 path (core2-link, Gi1/3)</t>
-        </is>
+      <c r="B19" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15">
         <v>3</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>VLAN10-NET</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>PAT (overload)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>VLAN 10 - End Devices</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>192.168.10.0/24</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>outside (Gi1/2)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>203.0.113.2</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>Interface overload</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>Via CORE-1 path; also covered by INTERNAL-LANS</t>
-        </is>
+      <c r="B20" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15">
         <v>4</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>SERVER-1 (Server0)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Static NAT</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>VLAN 20 - Servers</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>192.168.20.10/32</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>outside (Gi1/2)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>203.0.114.10</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>Published externally; ISP routes 203.0.114.0/24 to FW; HTTP (tcp/80) allowed by OUTSIDE-IN</t>
-        </is>
+      <c r="B21" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="48" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="38" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="39" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>436</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>437</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" x14ac:dyDescent="0.35">
+      <c r="A5" s="41">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>441</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>442</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>443</v>
+      </c>
+      <c r="N5" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" x14ac:dyDescent="0.35">
+      <c r="A6" s="41">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>445</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>446</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>447</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>450</v>
+      </c>
+      <c r="N6" s="41" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="41">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>454</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>455</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" x14ac:dyDescent="0.35">
+      <c r="A8" s="41">
+        <v>4</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>446</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>458</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>459</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>460</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>461</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>462</v>
+      </c>
+      <c r="N8" s="41" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A11" s="38" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>466</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>467</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" x14ac:dyDescent="0.35">
+      <c r="A13" s="41">
+        <v>1</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>468</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>469</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="41">
+        <v>2</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="39" t="s">
+        <v>473</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/IP_Addressing_Plan_for_Redundancy_arch.xlsx
+++ b/IP_Addressing_Plan_for_Redundancy_arch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akank\Downloads\cisco-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284EF510-81D6-4080-8DB3-DD21012D98EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEFBF0B-187D-4A79-87A2-2DFF8AE00209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="516">
   <si>
     <t xml:space="preserve">FIREWALL &amp; NAT </t>
   </si>
@@ -275,9 +275,6 @@
     <t>Via CORE-1 path; also covered by INTERNAL-LANS</t>
   </si>
   <si>
-    <t>SERVER-1 (Server0)</t>
-  </si>
-  <si>
     <t>Static NAT</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
     <t>Static (no DHCP)</t>
   </si>
   <si>
-    <t>Gateway on DIST-01/02 via HSRP (suggested: DIST-01 priority 110 active, DIST-02 100 standby).</t>
-  </si>
-  <si>
     <t>Servers</t>
   </si>
   <si>
@@ -431,9 +425,6 @@
     <t>192.168.30.255</t>
   </si>
   <si>
-    <t>No security devices are drawn in the diagram - add them as needed.</t>
-  </si>
-  <si>
     <t>Management</t>
   </si>
   <si>
@@ -521,18 +512,12 @@
     <t>DIST-01</t>
   </si>
   <si>
-    <t>HSRP Active, priority 110</t>
-  </si>
-  <si>
     <t>DIST-02 SVI</t>
   </si>
   <si>
     <t>DIST-02</t>
   </si>
   <si>
-    <t>HSRP Standby, priority 100</t>
-  </si>
-  <si>
     <t>PC0</t>
   </si>
   <si>
@@ -866,27 +851,18 @@
     <t>PC3</t>
   </si>
   <si>
-    <t>192.168.30.15/25</t>
-  </si>
-  <si>
     <t>0060.2FC0.4A51</t>
   </si>
   <si>
     <t>Printer1</t>
   </si>
   <si>
-    <t>192.168.30.16/26</t>
-  </si>
-  <si>
     <t>0001.645E.62B6</t>
   </si>
   <si>
     <t>Printer3</t>
   </si>
   <si>
-    <t>192.168.30.17/27</t>
-  </si>
-  <si>
     <t>0001.C771.5826</t>
   </si>
   <si>
@@ -923,12 +899,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Gateway</t>
-  </si>
-  <si>
-    <t>Default gateway for VLAN 99</t>
-  </si>
-  <si>
     <t>L3 Switch</t>
   </si>
   <si>
@@ -1491,6 +1461,138 @@
   </si>
   <si>
     <t>192.168.30.17</t>
+  </si>
+  <si>
+    <t>SERVER-0 (Server0)</t>
+  </si>
+  <si>
+    <t>192.168.30.15/24</t>
+  </si>
+  <si>
+    <t>192.168.30.16/24</t>
+  </si>
+  <si>
+    <t>192.168.30.17/24</t>
+  </si>
+  <si>
+    <t>192.168.10.16/24</t>
+  </si>
+  <si>
+    <t>192.168.10.19/24</t>
+  </si>
+  <si>
+    <t>192.168.10.21/24</t>
+  </si>
+  <si>
+    <t>192.168.10.23/24</t>
+  </si>
+  <si>
+    <t>192.168.10.24/24</t>
+  </si>
+  <si>
+    <t>192.168.10.25/24</t>
+  </si>
+  <si>
+    <t>192.168.10.26/24</t>
+  </si>
+  <si>
+    <t>192.168.10.28/24</t>
+  </si>
+  <si>
+    <t>192.168.10.30/24</t>
+  </si>
+  <si>
+    <t>192.168.10.31/24</t>
+  </si>
+  <si>
+    <t>192.168.20.12/24</t>
+  </si>
+  <si>
+    <t>192.168.20.13/24</t>
+  </si>
+  <si>
+    <t>192.168.20.14/24</t>
+  </si>
+  <si>
+    <t>192.168.20.15/24</t>
+  </si>
+  <si>
+    <t>192.168.20.16/24</t>
+  </si>
+  <si>
+    <t>192.168.99.1/24</t>
+  </si>
+  <si>
+    <t>192.168.99.2/24</t>
+  </si>
+  <si>
+    <t>192.168.99.11/24</t>
+  </si>
+  <si>
+    <t>192.168.99.12/24</t>
+  </si>
+  <si>
+    <t>192.168.99.21/24</t>
+  </si>
+  <si>
+    <t>192.168.99.22/24</t>
+  </si>
+  <si>
+    <t>192.168.99.23/24</t>
+  </si>
+  <si>
+    <t>192.168.99.24/24</t>
+  </si>
+  <si>
+    <t>192.168.99.25/24</t>
+  </si>
+  <si>
+    <t>192.168.99.26/24</t>
+  </si>
+  <si>
+    <t>192.168.99.27/24</t>
+  </si>
+  <si>
+    <t>192.168.99.28/24</t>
+  </si>
+  <si>
+    <t>192.168.99.31/24</t>
+  </si>
+  <si>
+    <t>192.168.99.32/24</t>
+  </si>
+  <si>
+    <t>192.168.99.33/24</t>
+  </si>
+  <si>
+    <t>192.168.99.34/24</t>
+  </si>
+  <si>
+    <t>192.168.99.35/24</t>
+  </si>
+  <si>
+    <t>192.168.99.36/24</t>
+  </si>
+  <si>
+    <t>192.168.99.37/24</t>
+  </si>
+  <si>
+    <t>192.168.99.38/24</t>
+  </si>
+  <si>
+    <t>192.168.99.39/24</t>
+  </si>
+  <si>
+    <t>192.168.99.40/24</t>
+  </si>
+  <si>
+    <t>192.168.99.50/24</t>
+  </si>
+  <si>
+    <t>/24</t>
+  </si>
+  <si>
+    <t>Gateway on CORE-01/02 via HSRP (suggested: CORE-01 priority 110 active, CORE-02 100 standby).</t>
   </si>
 </sst>
 </file>
@@ -1746,7 +1848,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1859,6 +1961,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2149,12 +2260,12 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2162,52 +2273,52 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R4" s="4" t="s">
         <v>16</v>
@@ -2218,46 +2329,46 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="E5" s="8">
         <v>24</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="N5" s="8">
         <v>254</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P5" s="8" t="s">
         <v>21</v>
@@ -2267,7 +2378,7 @@
         <v>16</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>110</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2275,46 +2386,46 @@
         <v>20</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="E6" s="8">
         <v>24</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>103</v>
-      </c>
       <c r="H6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="K6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="N6" s="8">
         <v>254</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P6" s="8" t="s">
         <v>21</v>
@@ -2324,7 +2435,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2332,46 +2443,46 @@
         <v>30</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="E7" s="8">
         <v>24</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>103</v>
-      </c>
       <c r="H7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="K7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="N7" s="8">
         <v>254</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P7" s="8" t="s">
         <v>21</v>
@@ -2380,65 +2491,63 @@
         <f>COUNTA('VLAN 30 - Security'!B5:B80)</f>
         <v>11</v>
       </c>
-      <c r="R7" s="7" t="s">
-        <v>128</v>
-      </c>
+      <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>99</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E8" s="8">
         <v>24</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>103</v>
-      </c>
       <c r="H8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="N8" s="8">
         <v>254</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P8" s="8" t="s">
         <v>21</v>
       </c>
       <c r="Q8" s="6">
         <f>COUNTA('VLAN 99 - Management'!B5:B80)</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -2446,13 +2555,13 @@
         <v>100</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E9" s="8">
         <v>30</v>
@@ -2461,31 +2570,31 @@
         <v>23</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="N9" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>147</v>
-      </c>
       <c r="O9" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P9" s="8" t="s">
         <v>21</v>
@@ -2495,7 +2604,7 @@
         <v>10</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2551,7 +2660,7 @@
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2608,16 +2717,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="F5" s="12">
         <v>10</v>
@@ -2628,11 +2737,11 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2640,16 +2749,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6" s="12">
         <v>10</v>
@@ -2663,25 +2772,23 @@
         <v>26</v>
       </c>
       <c r="M6" s="12"/>
-      <c r="N6" s="14" t="s">
-        <v>158</v>
-      </c>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7" s="12">
         <v>10</v>
@@ -2695,47 +2802,45 @@
         <v>26</v>
       </c>
       <c r="M7" s="12"/>
-      <c r="N7" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F8" s="15">
         <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H8" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="N8" s="7"/>
     </row>
@@ -2744,34 +2849,34 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F9" s="15">
         <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H9" s="43"/>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J9" s="43"/>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N9" s="7"/>
     </row>
@@ -2780,34 +2885,34 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F10" s="15">
         <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="N10" s="7"/>
     </row>
@@ -2816,34 +2921,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F11" s="15">
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
-        <v>183</v>
+        <v>476</v>
       </c>
       <c r="J11" s="43"/>
       <c r="K11" s="1"/>
       <c r="L11" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N11" s="7"/>
     </row>
@@ -2852,35 +2957,35 @@
         <v>13</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F12" s="19">
         <v>10</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="19" t="s">
-        <v>187</v>
+        <v>477</v>
       </c>
       <c r="J12" s="43"/>
       <c r="K12" s="19"/>
       <c r="L12" s="19" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M12" s="19"/>
       <c r="N12" s="21" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2888,34 +2993,34 @@
         <v>15</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F13" s="15">
         <v>10</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H13" s="43"/>
       <c r="I13" s="1" t="s">
-        <v>191</v>
+        <v>478</v>
       </c>
       <c r="J13" s="43"/>
       <c r="K13" s="1"/>
       <c r="L13" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N13" s="7"/>
     </row>
@@ -2924,34 +3029,34 @@
         <v>17</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F14" s="15">
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H14" s="43"/>
       <c r="I14" s="1" t="s">
-        <v>195</v>
+        <v>479</v>
       </c>
       <c r="J14" s="43"/>
       <c r="K14" s="1"/>
       <c r="L14" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="N14" s="7"/>
     </row>
@@ -2960,34 +3065,34 @@
         <v>18</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F15" s="15">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="1" t="s">
-        <v>198</v>
+        <v>480</v>
       </c>
       <c r="J15" s="43"/>
       <c r="K15" s="1"/>
       <c r="L15" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N15" s="7"/>
     </row>
@@ -2996,34 +3101,34 @@
         <v>19</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F16" s="15">
         <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H16" s="43"/>
       <c r="I16" s="1" t="s">
-        <v>202</v>
+        <v>481</v>
       </c>
       <c r="J16" s="43"/>
       <c r="K16" s="1"/>
       <c r="L16" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="N16" s="7"/>
     </row>
@@ -3032,34 +3137,34 @@
         <v>20</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F17" s="15">
         <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="1" t="s">
-        <v>205</v>
+        <v>482</v>
       </c>
       <c r="J17" s="43"/>
       <c r="K17" s="1"/>
       <c r="L17" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N17" s="7"/>
     </row>
@@ -3068,34 +3173,34 @@
         <v>22</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F18" s="15">
         <v>10</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="1" t="s">
-        <v>209</v>
+        <v>483</v>
       </c>
       <c r="J18" s="43"/>
       <c r="K18" s="1"/>
       <c r="L18" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="N18" s="7"/>
     </row>
@@ -3104,37 +3209,37 @@
         <v>24</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F19" s="15">
         <v>10</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H19" s="43"/>
       <c r="I19" s="1" t="s">
-        <v>215</v>
+        <v>484</v>
       </c>
       <c r="J19" s="43"/>
       <c r="K19" s="1"/>
       <c r="L19" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="N19" s="23" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3142,37 +3247,37 @@
         <v>25</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F20" s="15">
         <v>10</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H20" s="44"/>
       <c r="I20" s="1" t="s">
-        <v>220</v>
+        <v>485</v>
       </c>
       <c r="J20" s="44"/>
       <c r="K20" s="1"/>
       <c r="L20" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="N20" s="23" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3370,12 +3475,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3432,16 +3537,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F5" s="12">
         <v>20</v>
@@ -3452,11 +3557,11 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3464,16 +3569,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F6" s="12">
         <v>20</v>
@@ -3487,25 +3592,23 @@
         <v>26</v>
       </c>
       <c r="M6" s="12"/>
-      <c r="N6" s="14" t="s">
-        <v>158</v>
-      </c>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F7" s="12">
         <v>20</v>
@@ -3519,47 +3622,45 @@
         <v>26</v>
       </c>
       <c r="M7" s="12"/>
-      <c r="N7" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F8" s="15">
         <v>20</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H8" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="15" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N8" s="7"/>
     </row>
@@ -3568,26 +3669,26 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F9" s="15">
         <v>20</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H9" s="43"/>
       <c r="I9" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J9" s="43"/>
       <c r="K9" s="1"/>
@@ -3595,7 +3696,7 @@
         <v>26</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N9" s="7"/>
     </row>
@@ -3604,26 +3705,26 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F10" s="15">
         <v>20</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
-        <v>237</v>
+        <v>486</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="1"/>
@@ -3631,7 +3732,7 @@
         <v>26</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N10" s="7"/>
     </row>
@@ -3640,26 +3741,26 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F11" s="15">
         <v>20</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
-        <v>240</v>
+        <v>487</v>
       </c>
       <c r="J11" s="43"/>
       <c r="K11" s="1"/>
@@ -3667,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N11" s="7"/>
     </row>
@@ -3676,26 +3777,26 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F12" s="15">
         <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="1" t="s">
-        <v>244</v>
+        <v>488</v>
       </c>
       <c r="J12" s="43"/>
       <c r="K12" s="1"/>
@@ -3703,7 +3804,7 @@
         <v>26</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N12" s="7"/>
     </row>
@@ -3712,26 +3813,26 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F13" s="15">
         <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H13" s="43"/>
       <c r="I13" s="1" t="s">
-        <v>247</v>
+        <v>489</v>
       </c>
       <c r="J13" s="43"/>
       <c r="K13" s="1"/>
@@ -3739,7 +3840,7 @@
         <v>26</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="N13" s="7"/>
     </row>
@@ -3748,26 +3849,26 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F14" s="15">
         <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H14" s="44"/>
       <c r="I14" s="1" t="s">
-        <v>250</v>
+        <v>490</v>
       </c>
       <c r="J14" s="44"/>
       <c r="K14" s="1"/>
@@ -3775,7 +3876,7 @@
         <v>26</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N14" s="7"/>
     </row>
@@ -3958,12 +4059,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4020,16 +4121,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F5" s="12">
         <v>30</v>
@@ -4040,11 +4141,11 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4052,16 +4153,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F6" s="12">
         <v>30</v>
@@ -4075,25 +4176,23 @@
         <v>26</v>
       </c>
       <c r="M6" s="12"/>
-      <c r="N6" s="14" t="s">
-        <v>158</v>
-      </c>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F7" s="12">
         <v>30</v>
@@ -4107,47 +4206,45 @@
         <v>26</v>
       </c>
       <c r="M7" s="12"/>
-      <c r="N7" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F8" s="15">
         <v>30</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="H8" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J8" s="45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="15" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N8" s="7"/>
     </row>
@@ -4156,26 +4253,26 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F9" s="15">
         <v>30</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="H9" s="43"/>
       <c r="I9" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J9" s="43"/>
       <c r="K9" s="1"/>
@@ -4183,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="N9" s="7"/>
     </row>
@@ -4192,26 +4289,26 @@
         <v>6</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F10" s="15">
         <v>30</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="1"/>
@@ -4219,7 +4316,7 @@
         <v>26</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="N10" s="7"/>
     </row>
@@ -4228,26 +4325,26 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F11" s="15">
         <v>30</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J11" s="43"/>
       <c r="K11" s="1"/>
@@ -4255,7 +4352,7 @@
         <v>26</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="N11" s="7"/>
     </row>
@@ -4264,26 +4361,26 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F12" s="15">
         <v>30</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J12" s="43"/>
       <c r="K12" s="1"/>
@@ -4291,7 +4388,7 @@
         <v>26</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N12" s="7"/>
     </row>
@@ -4300,26 +4397,26 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F13" s="15">
         <v>30</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="H13" s="43"/>
       <c r="I13" s="1" t="s">
-        <v>273</v>
+        <v>473</v>
       </c>
       <c r="J13" s="43"/>
       <c r="K13" s="1"/>
@@ -4327,7 +4424,7 @@
         <v>26</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N13" s="7"/>
     </row>
@@ -4336,26 +4433,26 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F14" s="15">
         <v>30</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="H14" s="43"/>
       <c r="I14" s="1" t="s">
-        <v>276</v>
+        <v>474</v>
       </c>
       <c r="J14" s="43"/>
       <c r="K14" s="1"/>
@@ -4363,7 +4460,7 @@
         <v>26</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N14" s="7"/>
     </row>
@@ -4372,26 +4469,26 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F15" s="15">
         <v>30</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="1" t="s">
-        <v>279</v>
+        <v>475</v>
       </c>
       <c r="J15" s="43"/>
       <c r="K15" s="1"/>
@@ -4399,7 +4496,7 @@
         <v>26</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="N15" s="7"/>
     </row>
@@ -4503,17 +4600,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4521,22 +4618,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>10</v>
@@ -4548,13 +4645,13 @@
         <v>12</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>16</v>
@@ -4564,37 +4661,19 @@
       <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="F5" s="12">
-        <v>99</v>
-      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>293</v>
-      </c>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="13"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15">
@@ -4604,33 +4683,35 @@
         <v>19</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="F6" s="15">
         <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>491</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L6" s="16" t="s">
         <v>30</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N6" s="16"/>
     </row>
@@ -4642,35 +4723,37 @@
         <v>30</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="F7" s="15">
         <v>99</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>492</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N7" s="16"/>
     </row>
@@ -4679,41 +4762,43 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F8" s="15">
         <v>99</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>493</v>
+      </c>
       <c r="J8" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>19</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4721,41 +4806,43 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F9" s="15">
         <v>99</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>494</v>
+      </c>
       <c r="J9" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>30</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4763,38 +4850,40 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F10" s="15">
         <v>99</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>495</v>
+      </c>
       <c r="J10" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N10" s="16"/>
     </row>
@@ -4803,38 +4892,40 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F11" s="15">
         <v>99</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>496</v>
+      </c>
       <c r="J11" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N11" s="16"/>
     </row>
@@ -4843,38 +4934,40 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F12" s="15">
         <v>99</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>497</v>
+      </c>
       <c r="J12" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>316</v>
-      </c>
       <c r="M12" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N12" s="16"/>
     </row>
@@ -4883,38 +4976,40 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F13" s="15">
         <v>99</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I13" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>498</v>
+      </c>
       <c r="J13" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N13" s="16"/>
     </row>
@@ -4923,38 +5018,40 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F14" s="15">
         <v>99</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>499</v>
+      </c>
       <c r="J14" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N14" s="16"/>
     </row>
@@ -4963,38 +5060,40 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F15" s="15">
         <v>99</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I15" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I15" s="46" t="s">
+        <v>500</v>
+      </c>
       <c r="J15" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N15" s="16"/>
     </row>
@@ -5003,38 +5102,40 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F16" s="15">
         <v>99</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I16" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>501</v>
+      </c>
       <c r="J16" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N16" s="16"/>
     </row>
@@ -5043,38 +5144,40 @@
         <v>13</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F17" s="15">
         <v>99</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I17" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>502</v>
+      </c>
       <c r="J17" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N17" s="16"/>
     </row>
@@ -5083,38 +5186,40 @@
         <v>14</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F18" s="15">
         <v>99</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I18" s="46" t="s">
+        <v>503</v>
+      </c>
       <c r="J18" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N18" s="16"/>
     </row>
@@ -5123,38 +5228,40 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F19" s="15">
         <v>99</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>504</v>
+      </c>
       <c r="J19" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N19" s="16"/>
     </row>
@@ -5163,38 +5270,40 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F20" s="15">
         <v>99</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I20" s="46" t="s">
+        <v>505</v>
+      </c>
       <c r="J20" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N20" s="16"/>
     </row>
@@ -5203,38 +5312,40 @@
         <v>17</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F21" s="15">
         <v>99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>506</v>
+      </c>
       <c r="J21" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N21" s="16"/>
     </row>
@@ -5243,38 +5354,40 @@
         <v>18</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F22" s="15">
         <v>99</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I22" s="46" t="s">
+        <v>507</v>
+      </c>
       <c r="J22" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M22" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N22" s="16"/>
     </row>
@@ -5283,38 +5396,40 @@
         <v>19</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F23" s="15">
         <v>99</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I23" s="46" t="s">
+        <v>508</v>
+      </c>
       <c r="J23" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N23" s="16"/>
     </row>
@@ -5323,38 +5438,40 @@
         <v>20</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F24" s="15">
         <v>99</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I24" s="46" t="s">
+        <v>509</v>
+      </c>
       <c r="J24" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N24" s="16"/>
     </row>
@@ -5363,38 +5480,40 @@
         <v>21</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F25" s="15">
         <v>99</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>510</v>
+      </c>
       <c r="J25" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N25" s="16"/>
     </row>
@@ -5403,38 +5522,40 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F26" s="15">
         <v>99</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I26" s="46" t="s">
+        <v>511</v>
+      </c>
       <c r="J26" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N26" s="16"/>
     </row>
@@ -5443,38 +5564,40 @@
         <v>23</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F27" s="15">
         <v>99</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="I27" s="46" t="s">
+        <v>512</v>
+      </c>
       <c r="J27" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N27" s="16"/>
     </row>
@@ -5483,39 +5606,41 @@
         <v>24</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F28" s="27">
         <v>99</v>
       </c>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
+      <c r="I28" s="47" t="s">
+        <v>514</v>
+      </c>
       <c r="J28" s="29"/>
       <c r="K28" s="28" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="M28" s="27" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N28" s="28" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="O28" s="22"/>
       <c r="P28" s="30" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5523,41 +5648,43 @@
         <v>25</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="F29" s="17">
         <v>99</v>
       </c>
       <c r="G29" s="32" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="I29" s="32"/>
+        <v>101</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>513</v>
+      </c>
       <c r="J29" s="32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="L29" s="31" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N29" s="31" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5569,7 +5696,7 @@
       <c r="F30" s="15"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="48"/>
       <c r="J30" s="24"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
@@ -5585,7 +5712,7 @@
       <c r="F31" s="15"/>
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="48"/>
       <c r="J31" s="24"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
@@ -5601,7 +5728,7 @@
       <c r="F32" s="15"/>
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="48"/>
       <c r="J32" s="24"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
@@ -5617,7 +5744,7 @@
       <c r="F33" s="15"/>
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="48"/>
       <c r="J33" s="24"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
@@ -5633,7 +5760,7 @@
       <c r="F34" s="15"/>
       <c r="G34" s="24"/>
       <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="48"/>
       <c r="J34" s="24"/>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
@@ -5649,7 +5776,7 @@
       <c r="F35" s="15"/>
       <c r="G35" s="24"/>
       <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="48"/>
       <c r="J35" s="24"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
@@ -5665,7 +5792,7 @@
       <c r="F36" s="15"/>
       <c r="G36" s="24"/>
       <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
+      <c r="I36" s="48"/>
       <c r="J36" s="24"/>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
@@ -5674,12 +5801,12 @@
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5687,37 +5814,37 @@
         <v>3</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="M41" s="33"/>
       <c r="N41" s="4" t="s">
@@ -5735,35 +5862,35 @@
         <v>19</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G42" s="35" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="H42" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M42" s="33"/>
       <c r="N42" s="36" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -5777,31 +5904,31 @@
         <v>30</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="E43" s="34" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H43" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M43" s="33"/>
       <c r="N43" s="16"/>
@@ -5811,37 +5938,37 @@
         <v>3</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="H44" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M44" s="33"/>
       <c r="N44" s="16"/>
@@ -5851,37 +5978,37 @@
         <v>4</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E45" s="34" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="H45" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M45" s="33"/>
       <c r="N45" s="16"/>
@@ -5891,37 +6018,37 @@
         <v>5</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="H46" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M46" s="33"/>
       <c r="N46" s="16"/>
@@ -5931,37 +6058,37 @@
         <v>6</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H47" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M47" s="33"/>
       <c r="N47" s="16"/>
@@ -5971,37 +6098,37 @@
         <v>7</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E48" s="34" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="H48" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M48" s="33"/>
       <c r="N48" s="16"/>
@@ -6011,37 +6138,37 @@
         <v>8</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="H49" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M49" s="33"/>
       <c r="N49" s="16"/>
@@ -6051,37 +6178,37 @@
         <v>9</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="H50" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M50" s="33"/>
       <c r="N50" s="16"/>
@@ -6091,37 +6218,37 @@
         <v>10</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="H51" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M51" s="33"/>
       <c r="N51" s="16"/>
@@ -6131,37 +6258,37 @@
         <v>11</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="H52" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M52" s="33"/>
       <c r="N52" s="16"/>
@@ -6171,37 +6298,37 @@
         <v>12</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="H53" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M53" s="33"/>
       <c r="N53" s="16"/>
@@ -6211,37 +6338,37 @@
         <v>13</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="H54" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M54" s="33"/>
       <c r="N54" s="16"/>
@@ -6251,37 +6378,37 @@
         <v>14</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="H55" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M55" s="33"/>
       <c r="N55" s="16"/>
@@ -6291,37 +6418,37 @@
         <v>15</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="H56" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M56" s="33"/>
       <c r="N56" s="16"/>
@@ -6331,37 +6458,37 @@
         <v>16</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E57" s="34" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="H57" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M57" s="33"/>
       <c r="N57" s="16"/>
@@ -6371,37 +6498,37 @@
         <v>17</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="H58" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M58" s="33"/>
       <c r="N58" s="16"/>
@@ -6411,37 +6538,37 @@
         <v>18</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="H59" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M59" s="33"/>
       <c r="N59" s="16"/>
@@ -6451,37 +6578,37 @@
         <v>19</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="H60" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I60" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M60" s="33"/>
       <c r="N60" s="16"/>
@@ -6491,37 +6618,37 @@
         <v>20</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D61" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="H61" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="E61" s="34" t="s">
-        <v>426</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H61" s="34" t="s">
-        <v>348</v>
-      </c>
       <c r="I61" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M61" s="33"/>
       <c r="N61" s="16"/>
@@ -6531,37 +6658,37 @@
         <v>21</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="H62" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M62" s="33"/>
       <c r="N62" s="16"/>
@@ -6571,37 +6698,37 @@
         <v>22</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D63" s="34" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="H63" s="34" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M63" s="33"/>
       <c r="N63" s="16"/>
@@ -7108,28 +7235,28 @@
         <v>4</v>
       </c>
       <c r="B21" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="D21" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="E21" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>67</v>
       </c>
       <c r="G21" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="I21" s="16" t="s">
         <v>81</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -7163,12 +7290,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -7182,10 +7309,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="F4" s="40" t="s">
         <v>8</v>
@@ -7220,16 +7347,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="F5" s="41" t="s">
         <v>21</v>
@@ -7241,7 +7368,7 @@
         <v>23</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="J5" s="41" t="s">
         <v>21</v>
@@ -7253,10 +7380,10 @@
         <v>26</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="N5" s="41" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" x14ac:dyDescent="0.35">
@@ -7264,28 +7391,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="F6" s="41" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="J6" s="41" t="s">
         <v>21</v>
@@ -7297,10 +7424,10 @@
         <v>26</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="N6" s="41" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -7308,16 +7435,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F7" s="41" t="s">
         <v>21</v>
@@ -7332,13 +7459,13 @@
         <v>21</v>
       </c>
       <c r="L7" s="41" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="N7" s="41" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" x14ac:dyDescent="0.35">
@@ -7346,48 +7473,48 @@
         <v>4</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>37</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="F8" s="41" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="H8" s="41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="K8" s="41" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="L8" s="41" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N8" s="41" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A11" s="38" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -7395,13 +7522,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>16</v>
@@ -7412,16 +7539,16 @@
         <v>1</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="D13" s="41" t="s">
         <v>39</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
@@ -7429,21 +7556,21 @@
         <v>2</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" s="41" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="39" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
